--- a/Data/EXCEL/Transfer/salemon/202208/2237-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/2237-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97DE51F2-3C0B-4334-9723-1D458E668CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61725BA2-9E30-4236-90FB-6A1766DBF814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="2237-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,20 +1226,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q98"/>
+  <dimension ref="A1:Q99"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.875" customWidth="1"/>
-    <col min="2" max="5" width="8.25" customWidth="1"/>
-    <col min="6" max="7" width="9.125" customWidth="1"/>
-    <col min="8" max="8" width="9.5" customWidth="1"/>
-    <col min="9" max="10" width="11.875" customWidth="1"/>
-    <col min="11" max="11" width="9.5" customWidth="1"/>
-    <col min="12" max="12" width="10.75" customWidth="1"/>
-    <col min="13" max="13" width="9.5" customWidth="1"/>
-    <col min="14" max="15" width="11.875" customWidth="1"/>
-    <col min="16" max="16" width="9.5" customWidth="1"/>
-    <col min="17" max="17" width="11.875" customWidth="1"/>
+    <col min="1" max="1" width="14.125" customWidth="1"/>
+    <col min="2" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="15.25" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="15" width="17" customWidth="1"/>
+    <col min="16" max="16" width="13.5" customWidth="1"/>
+    <col min="17" max="17" width="16.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1384,1377 +1392,1377 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7">
-        <v>33.5</v>
+        <v>37</v>
       </c>
       <c r="C5" s="7">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="D5" s="7">
-        <v>37.950000000000003</v>
+        <v>38.5</v>
       </c>
       <c r="E5" s="7">
-        <v>32.5</v>
+        <v>36</v>
       </c>
       <c r="F5" s="8">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="G5" s="8">
-        <v>10.45</v>
+        <v>0.27</v>
       </c>
       <c r="H5" s="9">
-        <v>1.44</v>
-      </c>
-      <c r="I5" s="8">
-        <v>1.03</v>
+        <v>0.33</v>
+      </c>
+      <c r="I5" s="10">
+        <v>-77.099999999999994</v>
       </c>
       <c r="J5" s="8">
-        <v>144.4</v>
+        <v>621.1</v>
       </c>
       <c r="K5" s="9">
-        <v>4.01</v>
+        <v>4.34</v>
       </c>
       <c r="L5" s="8">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="M5" s="9">
-        <v>1.44</v>
-      </c>
-      <c r="N5" s="8">
-        <v>1.03</v>
+        <v>0.33</v>
+      </c>
+      <c r="N5" s="10">
+        <v>-77.099999999999994</v>
       </c>
       <c r="O5" s="8">
-        <v>144.4</v>
+        <v>621.1</v>
       </c>
       <c r="P5" s="9">
-        <v>4.01</v>
+        <v>4.34</v>
       </c>
       <c r="Q5" s="8">
-        <v>302</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B6" s="7">
-        <v>36.1</v>
+        <v>33.5</v>
       </c>
       <c r="C6" s="7">
-        <v>33.5</v>
+        <v>37</v>
       </c>
       <c r="D6" s="7">
-        <v>37.049999999999997</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="E6" s="7">
-        <v>33</v>
-      </c>
-      <c r="F6" s="10">
-        <v>-2.6</v>
-      </c>
-      <c r="G6" s="10">
-        <v>-7.2</v>
+        <v>32.5</v>
+      </c>
+      <c r="F6" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G6" s="8">
+        <v>10.45</v>
       </c>
       <c r="H6" s="9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="I6" s="8">
-        <v>1966.7</v>
+        <v>1.03</v>
       </c>
       <c r="J6" s="8">
-        <v>1124.3</v>
+        <v>144.4</v>
       </c>
       <c r="K6" s="9">
-        <v>2.57</v>
+        <v>4.01</v>
       </c>
       <c r="L6" s="8">
-        <v>530.5</v>
+        <v>302</v>
       </c>
       <c r="M6" s="9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="N6" s="8">
-        <v>1966.7</v>
+        <v>1.03</v>
       </c>
       <c r="O6" s="8">
-        <v>1124.3</v>
+        <v>144.4</v>
       </c>
       <c r="P6" s="9">
-        <v>2.57</v>
+        <v>4.01</v>
       </c>
       <c r="Q6" s="8">
-        <v>530.5</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B7" s="7">
-        <v>36.9</v>
+        <v>36.1</v>
       </c>
       <c r="C7" s="7">
-        <v>36.1</v>
+        <v>33.5</v>
       </c>
       <c r="D7" s="7">
-        <v>38.799999999999997</v>
+        <v>37.049999999999997</v>
       </c>
       <c r="E7" s="7">
-        <v>33.15</v>
+        <v>33</v>
       </c>
       <c r="F7" s="10">
-        <v>-0.8</v>
+        <v>-2.6</v>
       </c>
       <c r="G7" s="10">
-        <v>-2.17</v>
+        <v>-7.2</v>
       </c>
       <c r="H7" s="9">
-        <v>6.9099999999999995E-2</v>
-      </c>
-      <c r="I7" s="10">
-        <v>-17.899999999999999</v>
-      </c>
-      <c r="J7" s="10">
-        <v>-75.7</v>
+        <v>1.43</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1966.7</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1124.3</v>
       </c>
       <c r="K7" s="9">
-        <v>1.1399999999999999</v>
+        <v>2.57</v>
       </c>
       <c r="L7" s="8">
-        <v>291.89999999999998</v>
+        <v>530.5</v>
       </c>
       <c r="M7" s="9">
-        <v>6.9099999999999995E-2</v>
-      </c>
-      <c r="N7" s="10">
-        <v>-17.899999999999999</v>
-      </c>
-      <c r="O7" s="10">
-        <v>-75.7</v>
+        <v>1.43</v>
+      </c>
+      <c r="N7" s="8">
+        <v>1966.7</v>
+      </c>
+      <c r="O7" s="8">
+        <v>1124.3</v>
       </c>
       <c r="P7" s="9">
-        <v>1.1399999999999999</v>
+        <v>2.57</v>
       </c>
       <c r="Q7" s="8">
-        <v>291.89999999999998</v>
+        <v>530.5</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B8" s="7">
+        <v>36.9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>36.1</v>
+      </c>
+      <c r="D8" s="7">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="E8" s="7">
         <v>33.15</v>
       </c>
-      <c r="C8" s="7">
-        <v>36.9</v>
-      </c>
-      <c r="D8" s="7">
-        <v>45.5</v>
-      </c>
-      <c r="E8" s="7">
-        <v>32.9</v>
-      </c>
-      <c r="F8" s="8">
-        <v>3.75</v>
-      </c>
-      <c r="G8" s="8">
-        <v>11.31</v>
+      <c r="F8" s="10">
+        <v>-0.8</v>
+      </c>
+      <c r="G8" s="10">
+        <v>-2.17</v>
       </c>
       <c r="H8" s="9">
-        <v>8.4199999999999997E-2</v>
+        <v>6.9099999999999995E-2</v>
       </c>
       <c r="I8" s="10">
-        <v>-59.2</v>
-      </c>
-      <c r="J8" s="8">
-        <v>28931</v>
+        <v>-17.899999999999999</v>
+      </c>
+      <c r="J8" s="10">
+        <v>-75.7</v>
       </c>
       <c r="K8" s="9">
-        <v>1.07</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="L8" s="8">
-        <v>17711.8</v>
+        <v>291.89999999999998</v>
       </c>
       <c r="M8" s="9">
-        <v>8.4199999999999997E-2</v>
+        <v>6.9099999999999995E-2</v>
       </c>
       <c r="N8" s="10">
-        <v>-59.2</v>
-      </c>
-      <c r="O8" s="8">
-        <v>28931</v>
+        <v>-17.899999999999999</v>
+      </c>
+      <c r="O8" s="10">
+        <v>-75.7</v>
       </c>
       <c r="P8" s="9">
-        <v>1.07</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="Q8" s="8">
-        <v>17711.8</v>
+        <v>291.89999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" s="7">
-        <v>33.85</v>
+        <v>33.15</v>
       </c>
       <c r="C9" s="7">
-        <v>33.15</v>
+        <v>36.9</v>
       </c>
       <c r="D9" s="7">
-        <v>34.950000000000003</v>
+        <v>45.5</v>
       </c>
       <c r="E9" s="7">
-        <v>31.05</v>
-      </c>
-      <c r="F9" s="10">
-        <v>-0.7</v>
-      </c>
-      <c r="G9" s="10">
-        <v>-2.0699999999999998</v>
+        <v>32.9</v>
+      </c>
+      <c r="F9" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="G9" s="8">
+        <v>11.31</v>
       </c>
       <c r="H9" s="9">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="I9" s="8">
-        <v>424.4</v>
+        <v>8.4199999999999997E-2</v>
+      </c>
+      <c r="I9" s="10">
+        <v>-59.2</v>
       </c>
       <c r="J9" s="8">
-        <v>11954.4</v>
+        <v>28931</v>
       </c>
       <c r="K9" s="9">
-        <v>0.98499999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="L9" s="8">
-        <v>17142</v>
+        <v>17711.8</v>
       </c>
       <c r="M9" s="9">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="N9" s="8">
-        <v>424.4</v>
+        <v>8.4199999999999997E-2</v>
+      </c>
+      <c r="N9" s="10">
+        <v>-59.2</v>
       </c>
       <c r="O9" s="8">
-        <v>11954.4</v>
+        <v>28931</v>
       </c>
       <c r="P9" s="9">
-        <v>0.98499999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="Q9" s="8">
-        <v>17142</v>
+        <v>17711.8</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B10" s="7">
-        <v>34.549999999999997</v>
+        <v>33.85</v>
       </c>
       <c r="C10" s="7">
-        <v>33.85</v>
+        <v>33.15</v>
       </c>
       <c r="D10" s="7">
-        <v>35.35</v>
+        <v>34.950000000000003</v>
       </c>
       <c r="E10" s="7">
-        <v>33.35</v>
+        <v>31.05</v>
       </c>
       <c r="F10" s="10">
         <v>-0.7</v>
       </c>
       <c r="G10" s="10">
-        <v>-2.0299999999999998</v>
+        <v>-2.0699999999999998</v>
       </c>
       <c r="H10" s="9">
-        <v>3.9300000000000002E-2</v>
-      </c>
-      <c r="I10" s="10">
-        <v>-94.7</v>
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="I10" s="8">
+        <v>424.4</v>
       </c>
       <c r="J10" s="8">
-        <v>1383.4</v>
+        <v>11954.4</v>
       </c>
       <c r="K10" s="9">
-        <v>0.77800000000000002</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="L10" s="8">
-        <v>19359.8</v>
+        <v>17142</v>
       </c>
       <c r="M10" s="9">
-        <v>3.9300000000000002E-2</v>
-      </c>
-      <c r="N10" s="10">
-        <v>-94.7</v>
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="N10" s="8">
+        <v>424.4</v>
       </c>
       <c r="O10" s="8">
-        <v>1383.4</v>
+        <v>11954.4</v>
       </c>
       <c r="P10" s="9">
-        <v>0.77800000000000002</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="Q10" s="8">
-        <v>19359.8</v>
+        <v>17142</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B11" s="7">
-        <v>35.4</v>
+        <v>34.549999999999997</v>
       </c>
       <c r="C11" s="7">
-        <v>34.549999999999997</v>
+        <v>33.85</v>
       </c>
       <c r="D11" s="7">
-        <v>37.9</v>
+        <v>35.35</v>
       </c>
       <c r="E11" s="7">
-        <v>33.299999999999997</v>
+        <v>33.35</v>
       </c>
       <c r="F11" s="10">
-        <v>-0.85</v>
+        <v>-0.7</v>
       </c>
       <c r="G11" s="10">
-        <v>-2.4</v>
+        <v>-2.0299999999999998</v>
       </c>
       <c r="H11" s="9">
-        <v>0.73899999999999999</v>
+        <v>3.9300000000000002E-2</v>
       </c>
       <c r="I11" s="10">
-        <v>-65.7</v>
+        <v>-94.7</v>
       </c>
       <c r="J11" s="8">
-        <v>54646.7</v>
+        <v>1383.4</v>
       </c>
       <c r="K11" s="9">
-        <v>0.73899999999999999</v>
+        <v>0.77800000000000002</v>
       </c>
       <c r="L11" s="8">
-        <v>54646.7</v>
+        <v>19359.8</v>
       </c>
       <c r="M11" s="9">
-        <v>0.73899999999999999</v>
+        <v>3.9300000000000002E-2</v>
       </c>
       <c r="N11" s="10">
-        <v>-65.7</v>
+        <v>-94.7</v>
       </c>
       <c r="O11" s="8">
-        <v>54646.7</v>
+        <v>1383.4</v>
       </c>
       <c r="P11" s="9">
-        <v>0.73899999999999999</v>
+        <v>0.77800000000000002</v>
       </c>
       <c r="Q11" s="8">
-        <v>54646.7</v>
+        <v>19359.8</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B12" s="7">
-        <v>34.049999999999997</v>
+        <v>35.4</v>
       </c>
       <c r="C12" s="7">
-        <v>35.4</v>
+        <v>34.549999999999997</v>
       </c>
       <c r="D12" s="7">
-        <v>35.950000000000003</v>
+        <v>37.9</v>
       </c>
       <c r="E12" s="7">
-        <v>33.1</v>
-      </c>
-      <c r="F12" s="8">
-        <v>1.35</v>
-      </c>
-      <c r="G12" s="8">
-        <v>3.96</v>
+        <v>33.299999999999997</v>
+      </c>
+      <c r="F12" s="10">
+        <v>-0.85</v>
+      </c>
+      <c r="G12" s="10">
+        <v>-2.4</v>
       </c>
       <c r="H12" s="9">
-        <v>2.15</v>
-      </c>
-      <c r="I12" s="8">
-        <v>52564.5</v>
-      </c>
-      <c r="J12" s="10">
-        <v>-35.5</v>
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="I12" s="10">
+        <v>-65.7</v>
+      </c>
+      <c r="J12" s="8">
+        <v>54646.7</v>
       </c>
       <c r="K12" s="9">
-        <v>3.21</v>
-      </c>
-      <c r="L12" s="10">
-        <v>-5.98</v>
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="L12" s="8">
+        <v>54646.7</v>
       </c>
       <c r="M12" s="9">
-        <v>2.15</v>
-      </c>
-      <c r="N12" s="8">
-        <v>52564.5</v>
-      </c>
-      <c r="O12" s="10">
-        <v>-35.5</v>
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="N12" s="10">
+        <v>-65.7</v>
+      </c>
+      <c r="O12" s="8">
+        <v>54646.7</v>
       </c>
       <c r="P12" s="9">
-        <v>3.21</v>
-      </c>
-      <c r="Q12" s="10">
-        <v>-5.98</v>
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>54646.7</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B13" s="7">
-        <v>35.5</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="C13" s="7">
-        <v>34.049999999999997</v>
+        <v>35.4</v>
       </c>
       <c r="D13" s="7">
-        <v>36</v>
+        <v>35.950000000000003</v>
       </c>
       <c r="E13" s="7">
-        <v>32.9</v>
-      </c>
-      <c r="F13" s="10">
-        <v>-1.45</v>
-      </c>
-      <c r="G13" s="10">
-        <v>-4.08</v>
+        <v>33.1</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1.35</v>
+      </c>
+      <c r="G13" s="8">
+        <v>3.96</v>
       </c>
       <c r="H13" s="9">
-        <v>4.1000000000000003E-3</v>
-      </c>
-      <c r="I13" s="10">
-        <v>-28.5</v>
-      </c>
-      <c r="J13" s="8">
-        <v>59.8</v>
+        <v>2.15</v>
+      </c>
+      <c r="I13" s="8">
+        <v>52564.5</v>
+      </c>
+      <c r="J13" s="10">
+        <v>-35.5</v>
       </c>
       <c r="K13" s="9">
-        <v>1.06</v>
-      </c>
-      <c r="L13" s="8">
-        <v>1379.3</v>
+        <v>3.21</v>
+      </c>
+      <c r="L13" s="10">
+        <v>-5.98</v>
       </c>
       <c r="M13" s="9">
-        <v>4.1000000000000003E-3</v>
-      </c>
-      <c r="N13" s="10">
-        <v>-28.5</v>
-      </c>
-      <c r="O13" s="8">
-        <v>59.8</v>
+        <v>2.15</v>
+      </c>
+      <c r="N13" s="8">
+        <v>52564.5</v>
+      </c>
+      <c r="O13" s="10">
+        <v>-35.5</v>
       </c>
       <c r="P13" s="9">
-        <v>1.06</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>1379.3</v>
+        <v>3.21</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>-5.98</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B14" s="7">
-        <v>31.8</v>
+        <v>35.5</v>
       </c>
       <c r="C14" s="7">
-        <v>35.5</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D14" s="7">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="E14" s="7">
-        <v>28.5</v>
-      </c>
-      <c r="F14" s="8">
-        <v>3.7</v>
-      </c>
-      <c r="G14" s="8">
-        <v>11.64</v>
+        <v>32.9</v>
+      </c>
+      <c r="F14" s="10">
+        <v>-1.45</v>
+      </c>
+      <c r="G14" s="10">
+        <v>-4.08</v>
       </c>
       <c r="H14" s="9">
-        <v>5.7000000000000002E-3</v>
-      </c>
-      <c r="I14" s="8">
-        <v>145.5</v>
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="I14" s="10">
+        <v>-28.5</v>
       </c>
       <c r="J14" s="8">
-        <v>119.2</v>
+        <v>59.8</v>
       </c>
       <c r="K14" s="9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="L14" s="8">
-        <v>1428.4</v>
+        <v>1379.3</v>
       </c>
       <c r="M14" s="9">
-        <v>5.7000000000000002E-3</v>
-      </c>
-      <c r="N14" s="8">
-        <v>145.5</v>
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="N14" s="10">
+        <v>-28.5</v>
       </c>
       <c r="O14" s="8">
-        <v>119.2</v>
+        <v>59.8</v>
       </c>
       <c r="P14" s="9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Q14" s="8">
-        <v>1428.4</v>
+        <v>1379.3</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B15" s="7">
-        <v>36.25</v>
+        <v>31.8</v>
       </c>
       <c r="C15" s="7">
-        <v>31.8</v>
+        <v>35.5</v>
       </c>
       <c r="D15" s="7">
-        <v>37.450000000000003</v>
+        <v>37.5</v>
       </c>
       <c r="E15" s="7">
-        <v>31.6</v>
-      </c>
-      <c r="F15" s="10">
-        <v>-4.45</v>
-      </c>
-      <c r="G15" s="10">
-        <v>-12.28</v>
+        <v>28.5</v>
+      </c>
+      <c r="F15" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G15" s="8">
+        <v>11.64</v>
       </c>
       <c r="H15" s="9">
-        <v>2.3E-3</v>
-      </c>
-      <c r="I15" s="10">
-        <v>-94.9</v>
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="I15" s="8">
+        <v>145.5</v>
       </c>
       <c r="J15" s="8">
-        <v>109.9</v>
+        <v>119.2</v>
       </c>
       <c r="K15" s="9">
         <v>1.05</v>
       </c>
       <c r="L15" s="8">
-        <v>1479.8</v>
+        <v>1428.4</v>
       </c>
       <c r="M15" s="9">
-        <v>2.3E-3</v>
-      </c>
-      <c r="N15" s="10">
-        <v>-94.9</v>
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="N15" s="8">
+        <v>145.5</v>
       </c>
       <c r="O15" s="8">
-        <v>109.9</v>
+        <v>119.2</v>
       </c>
       <c r="P15" s="9">
         <v>1.05</v>
       </c>
       <c r="Q15" s="8">
-        <v>1479.8</v>
+        <v>1428.4</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B16" s="7">
-        <v>35.200000000000003</v>
+        <v>36.25</v>
       </c>
       <c r="C16" s="7">
-        <v>36.25</v>
+        <v>31.8</v>
       </c>
       <c r="D16" s="7">
-        <v>36.75</v>
+        <v>37.450000000000003</v>
       </c>
       <c r="E16" s="7">
-        <v>34</v>
-      </c>
-      <c r="F16" s="8">
+        <v>31.6</v>
+      </c>
+      <c r="F16" s="10">
+        <v>-4.45</v>
+      </c>
+      <c r="G16" s="10">
+        <v>-12.28</v>
+      </c>
+      <c r="H16" s="9">
+        <v>2.3E-3</v>
+      </c>
+      <c r="I16" s="10">
+        <v>-94.9</v>
+      </c>
+      <c r="J16" s="8">
+        <v>109.9</v>
+      </c>
+      <c r="K16" s="9">
         <v>1.05</v>
       </c>
-      <c r="G16" s="8">
-        <v>2.98</v>
-      </c>
-      <c r="H16" s="9">
-        <v>4.5699999999999998E-2</v>
-      </c>
-      <c r="I16" s="10">
-        <v>-92.2</v>
-      </c>
-      <c r="J16" s="8">
-        <v>1342.3</v>
-      </c>
-      <c r="K16" s="9">
-        <v>1.04</v>
-      </c>
       <c r="L16" s="8">
-        <v>1503.2</v>
+        <v>1479.8</v>
       </c>
       <c r="M16" s="9">
-        <v>4.5699999999999998E-2</v>
+        <v>2.3E-3</v>
       </c>
       <c r="N16" s="10">
-        <v>-92.2</v>
+        <v>-94.9</v>
       </c>
       <c r="O16" s="8">
-        <v>1342.3</v>
+        <v>109.9</v>
       </c>
       <c r="P16" s="9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Q16" s="8">
-        <v>1503.2</v>
+        <v>1479.8</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B17" s="7">
-        <v>37.15</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="C17" s="7">
-        <v>35.200000000000003</v>
+        <v>36.25</v>
       </c>
       <c r="D17" s="7">
-        <v>38.9</v>
+        <v>36.75</v>
       </c>
       <c r="E17" s="7">
-        <v>34.799999999999997</v>
-      </c>
-      <c r="F17" s="10">
-        <v>-1.95</v>
-      </c>
-      <c r="G17" s="10">
-        <v>-5.25</v>
+        <v>34</v>
+      </c>
+      <c r="F17" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="G17" s="8">
+        <v>2.98</v>
       </c>
       <c r="H17" s="9">
-        <v>0.59</v>
-      </c>
-      <c r="I17" s="8">
-        <v>406.1</v>
+        <v>4.5699999999999998E-2</v>
+      </c>
+      <c r="I17" s="10">
+        <v>-92.2</v>
       </c>
       <c r="J17" s="8">
-        <v>75571.8</v>
+        <v>1342.3</v>
       </c>
       <c r="K17" s="9">
-        <v>0.997</v>
+        <v>1.04</v>
       </c>
       <c r="L17" s="8">
-        <v>1511.5</v>
+        <v>1503.2</v>
       </c>
       <c r="M17" s="9">
-        <v>0.59</v>
-      </c>
-      <c r="N17" s="8">
-        <v>406.1</v>
+        <v>4.5699999999999998E-2</v>
+      </c>
+      <c r="N17" s="10">
+        <v>-92.2</v>
       </c>
       <c r="O17" s="8">
-        <v>75571.8</v>
+        <v>1342.3</v>
       </c>
       <c r="P17" s="9">
-        <v>0.997</v>
+        <v>1.04</v>
       </c>
       <c r="Q17" s="8">
-        <v>1511.5</v>
+        <v>1503.2</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B18" s="7">
-        <v>36.9</v>
+        <v>37.15</v>
       </c>
       <c r="C18" s="7">
-        <v>37.15</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="D18" s="7">
-        <v>43</v>
+        <v>38.9</v>
       </c>
       <c r="E18" s="7">
-        <v>33</v>
-      </c>
-      <c r="F18" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="G18" s="8">
-        <v>0.68</v>
+        <v>34.799999999999997</v>
+      </c>
+      <c r="F18" s="10">
+        <v>-1.95</v>
+      </c>
+      <c r="G18" s="10">
+        <v>-5.25</v>
       </c>
       <c r="H18" s="9">
-        <v>0.11700000000000001</v>
-      </c>
-      <c r="I18" s="10">
-        <v>-59</v>
+        <v>0.59</v>
+      </c>
+      <c r="I18" s="8">
+        <v>406.1</v>
       </c>
       <c r="J18" s="8">
-        <v>22768.6</v>
+        <v>75571.8</v>
       </c>
       <c r="K18" s="9">
-        <v>0.40699999999999997</v>
+        <v>0.997</v>
       </c>
       <c r="L18" s="8">
-        <v>566</v>
+        <v>1511.5</v>
       </c>
       <c r="M18" s="9">
-        <v>0.11700000000000001</v>
-      </c>
-      <c r="N18" s="10">
-        <v>-59</v>
+        <v>0.59</v>
+      </c>
+      <c r="N18" s="8">
+        <v>406.1</v>
       </c>
       <c r="O18" s="8">
-        <v>22768.6</v>
+        <v>75571.8</v>
       </c>
       <c r="P18" s="9">
-        <v>0.40699999999999997</v>
+        <v>0.997</v>
       </c>
       <c r="Q18" s="8">
-        <v>566</v>
+        <v>1511.5</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B19" s="7">
-        <v>39.950000000000003</v>
+        <v>36.9</v>
       </c>
       <c r="C19" s="7">
-        <v>36.9</v>
+        <v>37.15</v>
       </c>
       <c r="D19" s="7">
-        <v>40.450000000000003</v>
+        <v>43</v>
       </c>
       <c r="E19" s="7">
-        <v>26.8</v>
-      </c>
-      <c r="F19" s="10">
-        <v>-3.05</v>
-      </c>
-      <c r="G19" s="10">
-        <v>-7.63</v>
+        <v>33</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0.68</v>
       </c>
       <c r="H19" s="9">
-        <v>0.28399999999999997</v>
-      </c>
-      <c r="I19" s="8">
-        <v>97937.9</v>
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="I19" s="10">
+        <v>-59</v>
       </c>
       <c r="J19" s="8">
-        <v>26471</v>
+        <v>22768.6</v>
       </c>
       <c r="K19" s="9">
-        <v>0.28999999999999998</v>
+        <v>0.40699999999999997</v>
       </c>
       <c r="L19" s="8">
-        <v>379.1</v>
+        <v>566</v>
       </c>
       <c r="M19" s="9">
-        <v>0.28399999999999997</v>
-      </c>
-      <c r="N19" s="8">
-        <v>97937.9</v>
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="N19" s="10">
+        <v>-59</v>
       </c>
       <c r="O19" s="8">
-        <v>26471</v>
+        <v>22768.6</v>
       </c>
       <c r="P19" s="9">
-        <v>0.28999999999999998</v>
+        <v>0.40699999999999997</v>
       </c>
       <c r="Q19" s="8">
-        <v>379.1</v>
+        <v>566</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B20" s="7">
-        <v>40.4</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="C20" s="7">
-        <v>39.950000000000003</v>
+        <v>36.9</v>
       </c>
       <c r="D20" s="7">
-        <v>45</v>
+        <v>40.450000000000003</v>
       </c>
       <c r="E20" s="7">
-        <v>39.200000000000003</v>
+        <v>26.8</v>
       </c>
       <c r="F20" s="10">
-        <v>-0.45</v>
+        <v>-3.05</v>
       </c>
       <c r="G20" s="10">
-        <v>-1.1100000000000001</v>
+        <v>-7.63</v>
       </c>
       <c r="H20" s="9">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="I20" s="10">
-        <v>-83</v>
-      </c>
-      <c r="J20" s="10">
-        <v>-99.5</v>
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="I20" s="8">
+        <v>97937.9</v>
+      </c>
+      <c r="J20" s="8">
+        <v>26471</v>
       </c>
       <c r="K20" s="9">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="L20" s="10">
-        <v>-89.9</v>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L20" s="8">
+        <v>379.1</v>
       </c>
       <c r="M20" s="9">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="N20" s="10">
-        <v>-83</v>
-      </c>
-      <c r="O20" s="10">
-        <v>-99.5</v>
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="N20" s="8">
+        <v>97937.9</v>
+      </c>
+      <c r="O20" s="8">
+        <v>26471</v>
       </c>
       <c r="P20" s="9">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="Q20" s="10">
-        <v>-89.9</v>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>379.1</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B21" s="7">
-        <v>49.55</v>
+        <v>40.4</v>
       </c>
       <c r="C21" s="7">
-        <v>40.4</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="D21" s="7">
-        <v>50.6</v>
+        <v>45</v>
       </c>
       <c r="E21" s="7">
-        <v>39.799999999999997</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="F21" s="10">
-        <v>-9.15</v>
+        <v>-0.45</v>
       </c>
       <c r="G21" s="10">
-        <v>-18.47</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="H21" s="9">
-        <v>1.6999999999999999E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="I21" s="10">
-        <v>-35.5</v>
-      </c>
-      <c r="J21" s="8">
-        <v>850</v>
+        <v>-83</v>
+      </c>
+      <c r="J21" s="10">
+        <v>-99.5</v>
       </c>
       <c r="K21" s="9">
-        <v>5.7000000000000002E-3</v>
-      </c>
-      <c r="L21" s="8">
-        <v>124.8</v>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="L21" s="10">
+        <v>-89.9</v>
       </c>
       <c r="M21" s="9">
-        <v>1.6999999999999999E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="N21" s="10">
-        <v>-35.5</v>
-      </c>
-      <c r="O21" s="8">
-        <v>850</v>
+        <v>-83</v>
+      </c>
+      <c r="O21" s="10">
+        <v>-99.5</v>
       </c>
       <c r="P21" s="9">
-        <v>5.7000000000000002E-3</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>124.8</v>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>-89.9</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B22" s="7">
-        <v>36</v>
+        <v>49.55</v>
       </c>
       <c r="C22" s="7">
-        <v>49.55</v>
+        <v>40.4</v>
       </c>
       <c r="D22" s="7">
-        <v>51.5</v>
+        <v>50.6</v>
       </c>
       <c r="E22" s="7">
-        <v>34.549999999999997</v>
-      </c>
-      <c r="F22" s="8">
-        <v>13.55</v>
-      </c>
-      <c r="G22" s="8">
-        <v>37.64</v>
+        <v>39.799999999999997</v>
+      </c>
+      <c r="F22" s="10">
+        <v>-9.15</v>
+      </c>
+      <c r="G22" s="10">
+        <v>-18.47</v>
       </c>
       <c r="H22" s="9">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="I22" s="8">
-        <v>96.3</v>
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="I22" s="10">
+        <v>-35.5</v>
       </c>
       <c r="J22" s="8">
-        <v>45.6</v>
+        <v>850</v>
       </c>
       <c r="K22" s="9">
-        <v>4.0000000000000001E-3</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="L22" s="8">
-        <v>70.900000000000006</v>
+        <v>124.8</v>
       </c>
       <c r="M22" s="9">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="N22" s="8">
-        <v>96.3</v>
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="N22" s="10">
+        <v>-35.5</v>
       </c>
       <c r="O22" s="8">
-        <v>45.6</v>
+        <v>850</v>
       </c>
       <c r="P22" s="9">
-        <v>4.0000000000000001E-3</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="Q22" s="8">
-        <v>70.900000000000006</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B23" s="7">
-        <v>26.15</v>
+        <v>36</v>
       </c>
       <c r="C23" s="7">
-        <v>36</v>
+        <v>49.55</v>
       </c>
       <c r="D23" s="7">
-        <v>41.45</v>
+        <v>51.5</v>
       </c>
       <c r="E23" s="7">
-        <v>24.9</v>
+        <v>34.549999999999997</v>
       </c>
       <c r="F23" s="8">
-        <v>9.85</v>
+        <v>13.55</v>
       </c>
       <c r="G23" s="8">
-        <v>37.67</v>
+        <v>37.64</v>
       </c>
       <c r="H23" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="I23" s="10">
-        <v>-100</v>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="I23" s="8">
+        <v>96.3</v>
       </c>
       <c r="J23" s="8">
-        <v>154.69999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="K23" s="9">
-        <v>1.4E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="L23" s="8">
-        <v>154.69999999999999</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="M23" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="N23" s="10">
-        <v>-100</v>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="N23" s="8">
+        <v>96.3</v>
       </c>
       <c r="O23" s="8">
-        <v>154.69999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="P23" s="9">
-        <v>1.4E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="Q23" s="8">
-        <v>154.69999999999999</v>
+        <v>70.900000000000006</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B24" s="7">
-        <v>22.55</v>
+        <v>26.15</v>
       </c>
       <c r="C24" s="7">
-        <v>26.15</v>
+        <v>36</v>
       </c>
       <c r="D24" s="7">
-        <v>29.25</v>
+        <v>41.45</v>
       </c>
       <c r="E24" s="7">
-        <v>21.85</v>
+        <v>24.9</v>
       </c>
       <c r="F24" s="8">
-        <v>3.6</v>
+        <v>9.85</v>
       </c>
       <c r="G24" s="8">
-        <v>15.96</v>
+        <v>37.67</v>
       </c>
       <c r="H24" s="9">
-        <v>3.34</v>
-      </c>
-      <c r="I24" s="8">
-        <v>130444.5</v>
+        <v>1.4E-3</v>
+      </c>
+      <c r="I24" s="10">
+        <v>-100</v>
       </c>
       <c r="J24" s="8">
-        <v>72393.3</v>
+        <v>154.69999999999999</v>
       </c>
       <c r="K24" s="9">
-        <v>3.41</v>
+        <v>1.4E-3</v>
       </c>
       <c r="L24" s="8">
-        <v>113.5</v>
+        <v>154.69999999999999</v>
       </c>
       <c r="M24" s="9">
-        <v>3.34</v>
-      </c>
-      <c r="N24" s="8">
-        <v>130444.5</v>
+        <v>1.4E-3</v>
+      </c>
+      <c r="N24" s="10">
+        <v>-100</v>
       </c>
       <c r="O24" s="8">
-        <v>72393.3</v>
+        <v>154.69999999999999</v>
       </c>
       <c r="P24" s="9">
-        <v>3.41</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q24" s="8">
-        <v>113.5</v>
+        <v>154.69999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B25" s="7">
-        <v>18.5</v>
+        <v>22.55</v>
       </c>
       <c r="C25" s="7">
-        <v>22.55</v>
+        <v>26.15</v>
       </c>
       <c r="D25" s="7">
-        <v>22.6</v>
+        <v>29.25</v>
       </c>
       <c r="E25" s="7">
-        <v>18.5</v>
+        <v>21.85</v>
       </c>
       <c r="F25" s="8">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="G25" s="8">
-        <v>21.89</v>
+        <v>15.96</v>
       </c>
       <c r="H25" s="9">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="I25" s="10">
-        <v>-1.91</v>
-      </c>
-      <c r="J25" s="10">
-        <v>-23.6</v>
+        <v>3.34</v>
+      </c>
+      <c r="I25" s="8">
+        <v>130444.5</v>
+      </c>
+      <c r="J25" s="8">
+        <v>72393.3</v>
       </c>
       <c r="K25" s="9">
-        <v>7.1300000000000002E-2</v>
-      </c>
-      <c r="L25" s="10">
-        <v>-95.5</v>
+        <v>3.41</v>
+      </c>
+      <c r="L25" s="8">
+        <v>113.5</v>
       </c>
       <c r="M25" s="9">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="N25" s="10">
-        <v>-1.91</v>
-      </c>
-      <c r="O25" s="10">
-        <v>-23.6</v>
+        <v>3.34</v>
+      </c>
+      <c r="N25" s="8">
+        <v>130444.5</v>
+      </c>
+      <c r="O25" s="8">
+        <v>72393.3</v>
       </c>
       <c r="P25" s="9">
-        <v>7.1300000000000002E-2</v>
-      </c>
-      <c r="Q25" s="10">
-        <v>-95.5</v>
+        <v>3.41</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>113.5</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B26" s="7">
-        <v>18.149999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="C26" s="7">
+        <v>22.55</v>
+      </c>
+      <c r="D26" s="7">
+        <v>22.6</v>
+      </c>
+      <c r="E26" s="7">
         <v>18.5</v>
       </c>
-      <c r="D26" s="7">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="E26" s="7">
-        <v>18</v>
-      </c>
       <c r="F26" s="8">
-        <v>0.35</v>
+        <v>4.05</v>
       </c>
       <c r="G26" s="8">
-        <v>1.93</v>
+        <v>21.89</v>
       </c>
       <c r="H26" s="9">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="I26" s="8">
-        <v>135.1</v>
+      <c r="I26" s="10">
+        <v>-1.91</v>
       </c>
       <c r="J26" s="10">
-        <v>-96.1</v>
+        <v>-23.6</v>
       </c>
       <c r="K26" s="9">
-        <v>6.88E-2</v>
+        <v>7.1300000000000002E-2</v>
       </c>
       <c r="L26" s="10">
-        <v>-95.7</v>
+        <v>-95.5</v>
       </c>
       <c r="M26" s="9">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="N26" s="8">
-        <v>135.1</v>
+      <c r="N26" s="10">
+        <v>-1.91</v>
       </c>
       <c r="O26" s="10">
-        <v>-96.1</v>
+        <v>-23.6</v>
       </c>
       <c r="P26" s="9">
-        <v>6.88E-2</v>
+        <v>7.1300000000000002E-2</v>
       </c>
       <c r="Q26" s="10">
-        <v>-95.7</v>
+        <v>-95.5</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B27" s="7">
-        <v>17.899999999999999</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="C27" s="7">
-        <v>18.149999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="D27" s="7">
-        <v>18.8</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="E27" s="7">
-        <v>17.2</v>
+        <v>18</v>
       </c>
       <c r="F27" s="8">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="G27" s="8">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="H27" s="9">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="I27" s="10">
-        <v>-65</v>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="I27" s="8">
+        <v>135.1</v>
       </c>
       <c r="J27" s="10">
-        <v>-65.400000000000006</v>
+        <v>-96.1</v>
       </c>
       <c r="K27" s="9">
-        <v>6.6199999999999995E-2</v>
+        <v>6.88E-2</v>
       </c>
       <c r="L27" s="10">
-        <v>-95.6</v>
+        <v>-95.7</v>
       </c>
       <c r="M27" s="9">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="N27" s="10">
-        <v>-65</v>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="N27" s="8">
+        <v>135.1</v>
       </c>
       <c r="O27" s="10">
-        <v>-65.400000000000006</v>
+        <v>-96.1</v>
       </c>
       <c r="P27" s="9">
-        <v>6.6199999999999995E-2</v>
+        <v>6.88E-2</v>
       </c>
       <c r="Q27" s="10">
-        <v>-95.6</v>
+        <v>-95.7</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B28" s="7">
-        <v>17.149999999999999</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="C28" s="7">
-        <v>17.899999999999999</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="D28" s="7">
-        <v>19.600000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="E28" s="7">
-        <v>16.95</v>
+        <v>17.2</v>
       </c>
       <c r="F28" s="8">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="G28" s="8">
-        <v>4.37</v>
+        <v>1.4</v>
       </c>
       <c r="H28" s="9">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="I28" s="8">
-        <v>306.39999999999998</v>
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="I28" s="10">
+        <v>-65</v>
       </c>
       <c r="J28" s="10">
-        <v>-99</v>
+        <v>-65.400000000000006</v>
       </c>
       <c r="K28" s="9">
-        <v>6.5000000000000002E-2</v>
+        <v>6.6199999999999995E-2</v>
       </c>
       <c r="L28" s="10">
-        <v>-95.7</v>
+        <v>-95.6</v>
       </c>
       <c r="M28" s="9">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="N28" s="8">
-        <v>306.39999999999998</v>
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="N28" s="10">
+        <v>-65</v>
       </c>
       <c r="O28" s="10">
-        <v>-99</v>
+        <v>-65.400000000000006</v>
       </c>
       <c r="P28" s="9">
-        <v>6.5000000000000002E-2</v>
+        <v>6.6199999999999995E-2</v>
       </c>
       <c r="Q28" s="10">
-        <v>-95.7</v>
+        <v>-95.6</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B29" s="7">
-        <v>17.7</v>
+        <v>17.149999999999999</v>
       </c>
       <c r="C29" s="7">
-        <v>17.149999999999999</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="D29" s="7">
-        <v>18.2</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="E29" s="7">
-        <v>15.7</v>
-      </c>
-      <c r="F29" s="10">
-        <v>-0.55000000000000004</v>
-      </c>
-      <c r="G29" s="10">
-        <v>-3.11</v>
+        <v>16.95</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G29" s="8">
+        <v>4.37</v>
       </c>
       <c r="H29" s="9">
-        <v>8.0000000000000004E-4</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="I29" s="8">
-        <v>52.9</v>
+        <v>306.39999999999998</v>
       </c>
       <c r="J29" s="10">
-        <v>-84</v>
+        <v>-99</v>
       </c>
       <c r="K29" s="9">
-        <v>6.1899999999999997E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="L29" s="10">
-        <v>-94.9</v>
+        <v>-95.7</v>
       </c>
       <c r="M29" s="9">
-        <v>8.0000000000000004E-4</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="N29" s="8">
-        <v>52.9</v>
+        <v>306.39999999999998</v>
       </c>
       <c r="O29" s="10">
-        <v>-84</v>
+        <v>-99</v>
       </c>
       <c r="P29" s="9">
-        <v>6.1899999999999997E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="Q29" s="10">
-        <v>-94.9</v>
+        <v>-95.7</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B30" s="7">
-        <v>17.2</v>
+        <v>17.7</v>
       </c>
       <c r="C30" s="7">
-        <v>17.7</v>
+        <v>17.149999999999999</v>
       </c>
       <c r="D30" s="7">
-        <v>18.45</v>
+        <v>18.2</v>
       </c>
       <c r="E30" s="7">
-        <v>16.55</v>
-      </c>
-      <c r="F30" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="G30" s="8">
-        <v>2.91</v>
+        <v>15.7</v>
+      </c>
+      <c r="F30" s="10">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="G30" s="10">
+        <v>-3.11</v>
       </c>
       <c r="H30" s="9">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="I30" s="10">
-        <v>-52.3</v>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="I30" s="8">
+        <v>52.9</v>
       </c>
       <c r="J30" s="10">
-        <v>-99.9</v>
+        <v>-84</v>
       </c>
       <c r="K30" s="9">
-        <v>6.1100000000000002E-2</v>
+        <v>6.1899999999999997E-2</v>
       </c>
       <c r="L30" s="10">
         <v>-94.9</v>
       </c>
       <c r="M30" s="9">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="N30" s="10">
-        <v>-52.3</v>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="N30" s="8">
+        <v>52.9</v>
       </c>
       <c r="O30" s="10">
-        <v>-99.9</v>
+        <v>-84</v>
       </c>
       <c r="P30" s="9">
-        <v>6.1100000000000002E-2</v>
+        <v>6.1899999999999997E-2</v>
       </c>
       <c r="Q30" s="10">
         <v>-94.9</v>
@@ -2762,3211 +2770,3211 @@
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B31" s="7">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
       <c r="C31" s="7">
-        <v>17.2</v>
+        <v>17.7</v>
       </c>
       <c r="D31" s="7">
-        <v>17.7</v>
+        <v>18.45</v>
       </c>
       <c r="E31" s="7">
-        <v>14.8</v>
+        <v>16.55</v>
       </c>
       <c r="F31" s="8">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G31" s="8">
-        <v>2.38</v>
+        <v>2.91</v>
       </c>
       <c r="H31" s="9">
-        <v>1.1000000000000001E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="I31" s="10">
-        <v>-98.1</v>
+        <v>-52.3</v>
       </c>
       <c r="J31" s="10">
-        <v>-89.5</v>
+        <v>-99.9</v>
       </c>
       <c r="K31" s="9">
-        <v>6.0600000000000001E-2</v>
+        <v>6.1100000000000002E-2</v>
       </c>
       <c r="L31" s="10">
-        <v>-82.3</v>
+        <v>-94.9</v>
       </c>
       <c r="M31" s="9">
-        <v>1.1000000000000001E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="N31" s="10">
-        <v>-98.1</v>
+        <v>-52.3</v>
       </c>
       <c r="O31" s="10">
-        <v>-89.5</v>
+        <v>-99.9</v>
       </c>
       <c r="P31" s="9">
-        <v>6.0600000000000001E-2</v>
+        <v>6.1100000000000002E-2</v>
       </c>
       <c r="Q31" s="10">
-        <v>-82.3</v>
+        <v>-94.9</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B32" s="7">
-        <v>14.05</v>
+        <v>16.8</v>
       </c>
       <c r="C32" s="7">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
       <c r="D32" s="7">
-        <v>16.8</v>
+        <v>17.7</v>
       </c>
       <c r="E32" s="7">
-        <v>14.05</v>
+        <v>14.8</v>
       </c>
       <c r="F32" s="8">
-        <v>2.75</v>
+        <v>0.4</v>
       </c>
       <c r="G32" s="8">
-        <v>19.57</v>
+        <v>2.38</v>
       </c>
       <c r="H32" s="9">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="I32" s="8">
-        <v>31555.599999999999</v>
-      </c>
-      <c r="J32" s="8">
-        <v>4089.7</v>
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="I32" s="10">
+        <v>-98.1</v>
+      </c>
+      <c r="J32" s="10">
+        <v>-89.5</v>
       </c>
       <c r="K32" s="9">
-        <v>5.9499999999999997E-2</v>
+        <v>6.0600000000000001E-2</v>
       </c>
       <c r="L32" s="10">
-        <v>-82.1</v>
+        <v>-82.3</v>
       </c>
       <c r="M32" s="9">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="N32" s="8">
-        <v>31555.599999999999</v>
-      </c>
-      <c r="O32" s="8">
-        <v>4089.7</v>
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="N32" s="10">
+        <v>-98.1</v>
+      </c>
+      <c r="O32" s="10">
+        <v>-89.5</v>
       </c>
       <c r="P32" s="9">
-        <v>5.9499999999999997E-2</v>
+        <v>6.0600000000000001E-2</v>
       </c>
       <c r="Q32" s="10">
-        <v>-82.1</v>
+        <v>-82.3</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B33" s="7">
-        <v>17.75</v>
+        <v>14.05</v>
       </c>
       <c r="C33" s="7">
+        <v>16.8</v>
+      </c>
+      <c r="D33" s="7">
+        <v>16.8</v>
+      </c>
+      <c r="E33" s="7">
         <v>14.05</v>
       </c>
-      <c r="D33" s="7">
-        <v>18.059999999999999</v>
-      </c>
-      <c r="E33" s="7">
-        <v>10.32</v>
-      </c>
-      <c r="F33" s="10">
-        <v>-3.7</v>
-      </c>
-      <c r="G33" s="10">
-        <v>-20.85</v>
+      <c r="F33" s="8">
+        <v>2.75</v>
+      </c>
+      <c r="G33" s="8">
+        <v>19.57</v>
       </c>
       <c r="H33" s="9">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="I33" s="10">
-        <v>-90.1</v>
-      </c>
-      <c r="J33" s="10">
-        <v>-95.7</v>
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="I33" s="8">
+        <v>31555.599999999999</v>
+      </c>
+      <c r="J33" s="8">
+        <v>4089.7</v>
       </c>
       <c r="K33" s="9">
-        <v>2.5000000000000001E-3</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="L33" s="10">
-        <v>-99.2</v>
+        <v>-82.1</v>
       </c>
       <c r="M33" s="9">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="N33" s="10">
-        <v>-90.1</v>
-      </c>
-      <c r="O33" s="10">
-        <v>-95.7</v>
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="N33" s="8">
+        <v>31555.599999999999</v>
+      </c>
+      <c r="O33" s="8">
+        <v>4089.7</v>
       </c>
       <c r="P33" s="9">
-        <v>2.5000000000000001E-3</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="Q33" s="10">
-        <v>-99.2</v>
+        <v>-82.1</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B34" s="7">
-        <v>16.649999999999999</v>
+        <v>17.75</v>
       </c>
       <c r="C34" s="7">
-        <v>17.75</v>
+        <v>14.05</v>
       </c>
       <c r="D34" s="7">
-        <v>20.74</v>
+        <v>18.059999999999999</v>
       </c>
       <c r="E34" s="7">
-        <v>16.2</v>
-      </c>
-      <c r="F34" s="8">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G34" s="8">
-        <v>6.61</v>
+        <v>10.32</v>
+      </c>
+      <c r="F34" s="10">
+        <v>-3.7</v>
+      </c>
+      <c r="G34" s="10">
+        <v>-20.85</v>
       </c>
       <c r="H34" s="9">
-        <v>1.8E-3</v>
-      </c>
-      <c r="I34" s="8">
-        <v>243.4</v>
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="I34" s="10">
+        <v>-90.1</v>
       </c>
       <c r="J34" s="10">
-        <v>-55.1</v>
+        <v>-95.7</v>
       </c>
       <c r="K34" s="9">
-        <v>2.3E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="L34" s="10">
-        <v>-99.3</v>
+        <v>-99.2</v>
       </c>
       <c r="M34" s="9">
-        <v>1.8E-3</v>
-      </c>
-      <c r="N34" s="8">
-        <v>243.4</v>
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="N34" s="10">
+        <v>-90.1</v>
       </c>
       <c r="O34" s="10">
-        <v>-55.1</v>
+        <v>-95.7</v>
       </c>
       <c r="P34" s="9">
-        <v>2.3E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="Q34" s="10">
-        <v>-99.3</v>
+        <v>-99.2</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B35" s="7">
-        <v>17</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="C35" s="7">
-        <v>16.649999999999999</v>
+        <v>17.75</v>
       </c>
       <c r="D35" s="7">
-        <v>17.54</v>
+        <v>20.74</v>
       </c>
       <c r="E35" s="7">
-        <v>16.41</v>
-      </c>
-      <c r="F35" s="10">
-        <v>-0.35</v>
-      </c>
-      <c r="G35" s="10">
-        <v>-2.06</v>
+        <v>16.2</v>
+      </c>
+      <c r="F35" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G35" s="8">
+        <v>6.61</v>
       </c>
       <c r="H35" s="9">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="I35" s="10">
-        <v>-88.5</v>
+        <v>1.8E-3</v>
+      </c>
+      <c r="I35" s="8">
+        <v>243.4</v>
       </c>
       <c r="J35" s="10">
-        <v>-99.8</v>
+        <v>-55.1</v>
       </c>
       <c r="K35" s="9">
-        <v>5.0000000000000001E-4</v>
+        <v>2.3E-3</v>
       </c>
       <c r="L35" s="10">
-        <v>-99.8</v>
+        <v>-99.3</v>
       </c>
       <c r="M35" s="9">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="N35" s="10">
-        <v>-88.5</v>
+        <v>1.8E-3</v>
+      </c>
+      <c r="N35" s="8">
+        <v>243.4</v>
       </c>
       <c r="O35" s="10">
-        <v>-99.8</v>
+        <v>-55.1</v>
       </c>
       <c r="P35" s="9">
-        <v>5.0000000000000001E-4</v>
+        <v>2.3E-3</v>
       </c>
       <c r="Q35" s="10">
-        <v>-99.8</v>
+        <v>-99.3</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B36" s="7">
-        <v>17.86</v>
+        <v>17</v>
       </c>
       <c r="C36" s="7">
-        <v>17</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="D36" s="7">
-        <v>18.05</v>
+        <v>17.54</v>
       </c>
       <c r="E36" s="7">
-        <v>16.45</v>
+        <v>16.41</v>
       </c>
       <c r="F36" s="10">
-        <v>-0.86</v>
+        <v>-0.35</v>
       </c>
       <c r="G36" s="10">
-        <v>-4.82</v>
+        <v>-2.06</v>
       </c>
       <c r="H36" s="9">
-        <v>4.5999999999999999E-3</v>
-      </c>
-      <c r="I36" s="8">
-        <v>37.6</v>
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="I36" s="10">
+        <v>-88.5</v>
       </c>
       <c r="J36" s="10">
-        <v>-94.9</v>
+        <v>-99.8</v>
       </c>
       <c r="K36" s="9">
-        <v>1.6</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="L36" s="10">
-        <v>-5.84</v>
+        <v>-99.8</v>
       </c>
       <c r="M36" s="9">
-        <v>4.5999999999999999E-3</v>
-      </c>
-      <c r="N36" s="8">
-        <v>37.6</v>
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="N36" s="10">
+        <v>-88.5</v>
       </c>
       <c r="O36" s="10">
-        <v>-94.9</v>
+        <v>-99.8</v>
       </c>
       <c r="P36" s="9">
-        <v>1.6</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q36" s="10">
-        <v>-5.84</v>
+        <v>-99.8</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B37" s="7">
-        <v>14.35</v>
+        <v>17.86</v>
       </c>
       <c r="C37" s="7">
-        <v>17.86</v>
+        <v>17</v>
       </c>
       <c r="D37" s="7">
-        <v>21.77</v>
+        <v>18.05</v>
       </c>
       <c r="E37" s="7">
-        <v>13.55</v>
-      </c>
-      <c r="F37" s="8">
-        <v>3.51</v>
-      </c>
-      <c r="G37" s="8">
-        <v>24.46</v>
+        <v>16.45</v>
+      </c>
+      <c r="F37" s="10">
+        <v>-0.86</v>
+      </c>
+      <c r="G37" s="10">
+        <v>-4.82</v>
       </c>
       <c r="H37" s="9">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="I37" s="10">
-        <v>-95</v>
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="I37" s="8">
+        <v>37.6</v>
       </c>
       <c r="J37" s="10">
-        <v>-88.2</v>
+        <v>-94.9</v>
       </c>
       <c r="K37" s="9">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="L37" s="10">
-        <v>-0.85</v>
+        <v>-5.84</v>
       </c>
       <c r="M37" s="9">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="N37" s="10">
-        <v>-95</v>
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="N37" s="8">
+        <v>37.6</v>
       </c>
       <c r="O37" s="10">
-        <v>-88.2</v>
+        <v>-94.9</v>
       </c>
       <c r="P37" s="9">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q37" s="10">
-        <v>-0.85</v>
+        <v>-5.84</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B38" s="7">
-        <v>15.26</v>
+        <v>14.35</v>
       </c>
       <c r="C38" s="7">
-        <v>14.35</v>
+        <v>17.86</v>
       </c>
       <c r="D38" s="7">
-        <v>15.25</v>
+        <v>21.77</v>
       </c>
       <c r="E38" s="7">
-        <v>13.81</v>
-      </c>
-      <c r="F38" s="10">
-        <v>-0.91</v>
-      </c>
-      <c r="G38" s="10">
-        <v>-5.96</v>
+        <v>13.55</v>
+      </c>
+      <c r="F38" s="8">
+        <v>3.51</v>
+      </c>
+      <c r="G38" s="8">
+        <v>24.46</v>
       </c>
       <c r="H38" s="9">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="I38" s="8">
-        <v>1986</v>
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="I38" s="10">
+        <v>-95</v>
       </c>
       <c r="J38" s="10">
-        <v>-95.5</v>
+        <v>-88.2</v>
       </c>
       <c r="K38" s="9">
         <v>1.59</v>
       </c>
-      <c r="L38" s="8">
-        <v>0.71</v>
+      <c r="L38" s="10">
+        <v>-0.85</v>
       </c>
       <c r="M38" s="9">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="N38" s="8">
-        <v>1986</v>
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="N38" s="10">
+        <v>-95</v>
       </c>
       <c r="O38" s="10">
-        <v>-95.5</v>
+        <v>-88.2</v>
       </c>
       <c r="P38" s="9">
         <v>1.59</v>
       </c>
-      <c r="Q38" s="8">
-        <v>0.71</v>
+      <c r="Q38" s="10">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B39" s="7">
-        <v>15.65</v>
+        <v>15.26</v>
       </c>
       <c r="C39" s="7">
-        <v>15.26</v>
+        <v>14.35</v>
       </c>
       <c r="D39" s="7">
-        <v>16.190000000000001</v>
+        <v>15.25</v>
       </c>
       <c r="E39" s="7">
-        <v>14.95</v>
+        <v>13.81</v>
       </c>
       <c r="F39" s="10">
-        <v>-0.39</v>
+        <v>-0.91</v>
       </c>
       <c r="G39" s="10">
-        <v>-2.4900000000000002</v>
+        <v>-5.96</v>
       </c>
       <c r="H39" s="9">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="I39" s="10">
-        <v>-99</v>
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="I39" s="8">
+        <v>1986</v>
       </c>
       <c r="J39" s="10">
-        <v>-82.3</v>
+        <v>-95.5</v>
       </c>
       <c r="K39" s="9">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="L39" s="8">
-        <v>1602.2</v>
+        <v>0.71</v>
       </c>
       <c r="M39" s="9">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="N39" s="10">
-        <v>-99</v>
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="N39" s="8">
+        <v>1986</v>
       </c>
       <c r="O39" s="10">
-        <v>-82.3</v>
+        <v>-95.5</v>
       </c>
       <c r="P39" s="9">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="Q39" s="8">
-        <v>1602.2</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B40" s="7">
-        <v>17</v>
+        <v>15.65</v>
       </c>
       <c r="C40" s="7">
-        <v>15.65</v>
+        <v>15.26</v>
       </c>
       <c r="D40" s="7">
-        <v>17.09</v>
+        <v>16.190000000000001</v>
       </c>
       <c r="E40" s="7">
-        <v>15.01</v>
+        <v>14.95</v>
       </c>
       <c r="F40" s="10">
-        <v>-1.35</v>
+        <v>-0.39</v>
       </c>
       <c r="G40" s="10">
-        <v>-7.94</v>
+        <v>-2.4900000000000002</v>
       </c>
       <c r="H40" s="9">
-        <v>0.308</v>
-      </c>
-      <c r="I40" s="8">
-        <v>6195.1</v>
-      </c>
-      <c r="J40" s="8">
-        <v>5180.1000000000004</v>
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="I40" s="10">
+        <v>-99</v>
+      </c>
+      <c r="J40" s="10">
+        <v>-82.3</v>
       </c>
       <c r="K40" s="9">
         <v>1.52</v>
       </c>
       <c r="L40" s="8">
-        <v>2031</v>
+        <v>1602.2</v>
       </c>
       <c r="M40" s="9">
-        <v>0.308</v>
-      </c>
-      <c r="N40" s="8">
-        <v>6195.1</v>
-      </c>
-      <c r="O40" s="8">
-        <v>5180.1000000000004</v>
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="N40" s="10">
+        <v>-99</v>
+      </c>
+      <c r="O40" s="10">
+        <v>-82.3</v>
       </c>
       <c r="P40" s="9">
         <v>1.52</v>
       </c>
       <c r="Q40" s="8">
-        <v>2031</v>
+        <v>1602.2</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B41" s="7">
-        <v>16.940000000000001</v>
+        <v>17</v>
       </c>
       <c r="C41" s="7">
-        <v>17</v>
+        <v>15.65</v>
       </c>
       <c r="D41" s="7">
-        <v>17.71</v>
+        <v>17.09</v>
       </c>
       <c r="E41" s="7">
-        <v>16.66</v>
-      </c>
-      <c r="F41" s="8">
-        <v>0.06</v>
-      </c>
-      <c r="G41" s="8">
-        <v>0.35</v>
+        <v>15.01</v>
+      </c>
+      <c r="F41" s="10">
+        <v>-1.35</v>
+      </c>
+      <c r="G41" s="10">
+        <v>-7.94</v>
       </c>
       <c r="H41" s="9">
-        <v>4.8999999999999998E-3</v>
-      </c>
-      <c r="I41" s="10">
-        <v>-99.4</v>
+        <v>0.308</v>
+      </c>
+      <c r="I41" s="8">
+        <v>6195.1</v>
       </c>
       <c r="J41" s="8">
-        <v>31.1</v>
+        <v>5180.1000000000004</v>
       </c>
       <c r="K41" s="9">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="L41" s="8">
-        <v>1750.8</v>
+        <v>2031</v>
       </c>
       <c r="M41" s="9">
-        <v>4.8999999999999998E-3</v>
-      </c>
-      <c r="N41" s="10">
-        <v>-99.4</v>
+        <v>0.308</v>
+      </c>
+      <c r="N41" s="8">
+        <v>6195.1</v>
       </c>
       <c r="O41" s="8">
-        <v>31.1</v>
+        <v>5180.1000000000004</v>
       </c>
       <c r="P41" s="9">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="Q41" s="8">
-        <v>1750.8</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B42" s="7">
-        <v>17.350000000000001</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="C42" s="7">
-        <v>16.940000000000001</v>
+        <v>17</v>
       </c>
       <c r="D42" s="7">
-        <v>17.399999999999999</v>
+        <v>17.71</v>
       </c>
       <c r="E42" s="7">
-        <v>16.510000000000002</v>
-      </c>
-      <c r="F42" s="10">
-        <v>-0.41</v>
-      </c>
-      <c r="G42" s="10">
-        <v>-2.36</v>
+        <v>16.66</v>
+      </c>
+      <c r="F42" s="8">
+        <v>0.06</v>
+      </c>
+      <c r="G42" s="8">
+        <v>0.35</v>
       </c>
       <c r="H42" s="9">
-        <v>0.86499999999999999</v>
-      </c>
-      <c r="I42" s="8">
-        <v>8413</v>
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="I42" s="10">
+        <v>-99.4</v>
       </c>
       <c r="J42" s="8">
-        <v>47951.1</v>
+        <v>31.1</v>
       </c>
       <c r="K42" s="9">
         <v>1.21</v>
       </c>
       <c r="L42" s="8">
-        <v>1854.9</v>
+        <v>1750.8</v>
       </c>
       <c r="M42" s="9">
-        <v>0.86499999999999999</v>
-      </c>
-      <c r="N42" s="8">
-        <v>8413</v>
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="N42" s="10">
+        <v>-99.4</v>
       </c>
       <c r="O42" s="8">
-        <v>47951.1</v>
+        <v>31.1</v>
       </c>
       <c r="P42" s="9">
         <v>1.21</v>
       </c>
       <c r="Q42" s="8">
-        <v>1854.9</v>
+        <v>1750.8</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B43" s="7">
-        <v>19.07</v>
+        <v>17.350000000000001</v>
       </c>
       <c r="C43" s="7">
-        <v>17.350000000000001</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="D43" s="7">
-        <v>19.2</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="E43" s="7">
-        <v>17.309999999999999</v>
+        <v>16.510000000000002</v>
       </c>
       <c r="F43" s="10">
-        <v>-1.72</v>
+        <v>-0.41</v>
       </c>
       <c r="G43" s="10">
-        <v>-9.02</v>
+        <v>-2.36</v>
       </c>
       <c r="H43" s="9">
-        <v>1.0200000000000001E-2</v>
+        <v>0.86499999999999999</v>
       </c>
       <c r="I43" s="8">
-        <v>647</v>
+        <v>8413</v>
       </c>
       <c r="J43" s="8">
-        <v>620.6</v>
+        <v>47951.1</v>
       </c>
       <c r="K43" s="9">
-        <v>0.34300000000000003</v>
+        <v>1.21</v>
       </c>
       <c r="L43" s="8">
-        <v>471.3</v>
+        <v>1854.9</v>
       </c>
       <c r="M43" s="9">
-        <v>1.0200000000000001E-2</v>
+        <v>0.86499999999999999</v>
       </c>
       <c r="N43" s="8">
-        <v>647</v>
+        <v>8413</v>
       </c>
       <c r="O43" s="8">
-        <v>620.6</v>
+        <v>47951.1</v>
       </c>
       <c r="P43" s="9">
-        <v>0.34300000000000003</v>
+        <v>1.21</v>
       </c>
       <c r="Q43" s="8">
-        <v>471.3</v>
+        <v>1854.9</v>
       </c>
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B44" s="7">
-        <v>19.02</v>
+        <v>19.07</v>
       </c>
       <c r="C44" s="7">
-        <v>19.07</v>
+        <v>17.350000000000001</v>
       </c>
       <c r="D44" s="7">
-        <v>21.3</v>
+        <v>19.2</v>
       </c>
       <c r="E44" s="7">
-        <v>18.93</v>
-      </c>
-      <c r="F44" s="8">
-        <v>0.05</v>
-      </c>
-      <c r="G44" s="8">
-        <v>0.26</v>
+        <v>17.309999999999999</v>
+      </c>
+      <c r="F44" s="10">
+        <v>-1.72</v>
+      </c>
+      <c r="G44" s="10">
+        <v>-9.02</v>
       </c>
       <c r="H44" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="I44" s="10">
-        <v>-67.400000000000006</v>
-      </c>
-      <c r="J44" s="10">
-        <v>-97.4</v>
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="I44" s="8">
+        <v>647</v>
+      </c>
+      <c r="J44" s="8">
+        <v>620.6</v>
       </c>
       <c r="K44" s="9">
-        <v>0.33200000000000002</v>
+        <v>0.34300000000000003</v>
       </c>
       <c r="L44" s="8">
-        <v>467.7</v>
+        <v>471.3</v>
       </c>
       <c r="M44" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="N44" s="10">
-        <v>-67.400000000000006</v>
-      </c>
-      <c r="O44" s="10">
-        <v>-97.4</v>
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="N44" s="8">
+        <v>647</v>
+      </c>
+      <c r="O44" s="8">
+        <v>620.6</v>
       </c>
       <c r="P44" s="9">
-        <v>0.33200000000000002</v>
+        <v>0.34300000000000003</v>
       </c>
       <c r="Q44" s="8">
-        <v>467.7</v>
+        <v>471.3</v>
       </c>
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B45" s="7">
-        <v>19.600000000000001</v>
+        <v>19.02</v>
       </c>
       <c r="C45" s="7">
-        <v>19.02</v>
+        <v>19.07</v>
       </c>
       <c r="D45" s="7">
-        <v>19.989999999999998</v>
+        <v>21.3</v>
       </c>
       <c r="E45" s="7">
-        <v>18.809999999999999</v>
-      </c>
-      <c r="F45" s="10">
-        <v>-0.57999999999999996</v>
-      </c>
-      <c r="G45" s="10">
-        <v>-2.96</v>
+        <v>18.93</v>
+      </c>
+      <c r="F45" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="G45" s="8">
+        <v>0.26</v>
       </c>
       <c r="H45" s="9">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="I45" s="8">
-        <v>2.96</v>
-      </c>
-      <c r="J45" s="8">
-        <v>197.8</v>
+        <v>1.4E-3</v>
+      </c>
+      <c r="I45" s="10">
+        <v>-67.400000000000006</v>
+      </c>
+      <c r="J45" s="10">
+        <v>-97.4</v>
       </c>
       <c r="K45" s="9">
-        <v>0.33100000000000002</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="L45" s="8">
-        <v>5180.8999999999996</v>
+        <v>467.7</v>
       </c>
       <c r="M45" s="9">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="N45" s="8">
-        <v>2.96</v>
-      </c>
-      <c r="O45" s="8">
-        <v>197.8</v>
+        <v>1.4E-3</v>
+      </c>
+      <c r="N45" s="10">
+        <v>-67.400000000000006</v>
+      </c>
+      <c r="O45" s="10">
+        <v>-97.4</v>
       </c>
       <c r="P45" s="9">
-        <v>0.33100000000000002</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="Q45" s="8">
-        <v>5180.8999999999996</v>
+        <v>467.7</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B46" s="7">
-        <v>19.559999999999999</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="C46" s="7">
-        <v>19.600000000000001</v>
+        <v>19.02</v>
       </c>
       <c r="D46" s="7">
-        <v>20.100000000000001</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="E46" s="7">
-        <v>19</v>
-      </c>
-      <c r="F46" s="8">
-        <v>0.04</v>
-      </c>
-      <c r="G46" s="8">
-        <v>0.2</v>
+        <v>18.809999999999999</v>
+      </c>
+      <c r="F46" s="10">
+        <v>-0.57999999999999996</v>
+      </c>
+      <c r="G46" s="10">
+        <v>-2.96</v>
       </c>
       <c r="H46" s="9">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="I46" s="10">
-        <v>-98.7</v>
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="I46" s="8">
+        <v>2.96</v>
       </c>
       <c r="J46" s="8">
-        <v>26.6</v>
+        <v>197.8</v>
       </c>
       <c r="K46" s="9">
-        <v>0.32700000000000001</v>
+        <v>0.33100000000000002</v>
       </c>
       <c r="L46" s="8">
-        <v>6613.3</v>
+        <v>5180.8999999999996</v>
       </c>
       <c r="M46" s="9">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="N46" s="10">
-        <v>-98.7</v>
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="N46" s="8">
+        <v>2.96</v>
       </c>
       <c r="O46" s="8">
-        <v>26.6</v>
+        <v>197.8</v>
       </c>
       <c r="P46" s="9">
-        <v>0.32700000000000001</v>
+        <v>0.33100000000000002</v>
       </c>
       <c r="Q46" s="8">
-        <v>6613.3</v>
+        <v>5180.8999999999996</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B47" s="7">
-        <v>19.02</v>
+        <v>19.559999999999999</v>
       </c>
       <c r="C47" s="7">
-        <v>19.559999999999999</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="D47" s="7">
-        <v>21.29</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="E47" s="7">
-        <v>18.510000000000002</v>
+        <v>19</v>
       </c>
       <c r="F47" s="8">
-        <v>0.54</v>
+        <v>0.04</v>
       </c>
       <c r="G47" s="8">
-        <v>2.84</v>
+        <v>0.2</v>
       </c>
       <c r="H47" s="9">
-        <v>0.32300000000000001</v>
-      </c>
-      <c r="I47" s="8">
-        <v>258.39999999999998</v>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I47" s="10">
+        <v>-98.7</v>
       </c>
       <c r="J47" s="8">
-        <v>19235.3</v>
+        <v>26.6</v>
       </c>
       <c r="K47" s="9">
-        <v>0.32300000000000001</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="L47" s="8">
-        <v>19235.3</v>
+        <v>6613.3</v>
       </c>
       <c r="M47" s="9">
-        <v>0.32300000000000001</v>
-      </c>
-      <c r="N47" s="8">
-        <v>258.39999999999998</v>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="N47" s="10">
+        <v>-98.7</v>
       </c>
       <c r="O47" s="8">
-        <v>19235.3</v>
+        <v>26.6</v>
       </c>
       <c r="P47" s="9">
-        <v>0.32300000000000001</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="Q47" s="8">
-        <v>19235.3</v>
+        <v>6613.3</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B48" s="7">
-        <v>20.3</v>
+        <v>19.02</v>
       </c>
       <c r="C48" s="7">
-        <v>19.02</v>
+        <v>19.559999999999999</v>
       </c>
       <c r="D48" s="7">
-        <v>20.440000000000001</v>
+        <v>21.29</v>
       </c>
       <c r="E48" s="7">
-        <v>18.809999999999999</v>
-      </c>
-      <c r="F48" s="10">
-        <v>-1.28</v>
-      </c>
-      <c r="G48" s="10">
-        <v>-6.31</v>
+        <v>18.510000000000002</v>
+      </c>
+      <c r="F48" s="8">
+        <v>0.54</v>
+      </c>
+      <c r="G48" s="8">
+        <v>2.84</v>
       </c>
       <c r="H48" s="9">
-        <v>9.01E-2</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="I48" s="8">
-        <v>216.2</v>
+        <v>258.39999999999998</v>
       </c>
       <c r="J48" s="8">
-        <v>634.9</v>
+        <v>19235.3</v>
       </c>
       <c r="K48" s="9">
-        <v>1.7</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="L48" s="8">
-        <v>186.4</v>
+        <v>19235.3</v>
       </c>
       <c r="M48" s="9">
-        <v>9.01E-2</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="N48" s="8">
-        <v>216.2</v>
+        <v>258.39999999999998</v>
       </c>
       <c r="O48" s="8">
-        <v>634.9</v>
+        <v>19235.3</v>
       </c>
       <c r="P48" s="9">
-        <v>1.7</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="Q48" s="8">
-        <v>186.4</v>
+        <v>19235.3</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B49" s="7">
-        <v>20.79</v>
+        <v>20.3</v>
       </c>
       <c r="C49" s="7">
-        <v>20.3</v>
+        <v>19.02</v>
       </c>
       <c r="D49" s="7">
-        <v>21.19</v>
+        <v>20.440000000000001</v>
       </c>
       <c r="E49" s="7">
-        <v>19.420000000000002</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="F49" s="10">
-        <v>-0.49</v>
+        <v>-1.28</v>
       </c>
       <c r="G49" s="10">
-        <v>-2.36</v>
+        <v>-6.31</v>
       </c>
       <c r="H49" s="9">
-        <v>2.8500000000000001E-2</v>
-      </c>
-      <c r="I49" s="10">
-        <v>-42.6</v>
-      </c>
-      <c r="J49" s="10">
-        <v>-85.1</v>
+        <v>9.01E-2</v>
+      </c>
+      <c r="I49" s="8">
+        <v>216.2</v>
+      </c>
+      <c r="J49" s="8">
+        <v>634.9</v>
       </c>
       <c r="K49" s="9">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="L49" s="8">
-        <v>177</v>
+        <v>186.4</v>
       </c>
       <c r="M49" s="9">
-        <v>2.8500000000000001E-2</v>
-      </c>
-      <c r="N49" s="10">
-        <v>-42.6</v>
-      </c>
-      <c r="O49" s="10">
-        <v>-85.1</v>
+        <v>9.01E-2</v>
+      </c>
+      <c r="N49" s="8">
+        <v>216.2</v>
+      </c>
+      <c r="O49" s="8">
+        <v>634.9</v>
       </c>
       <c r="P49" s="9">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Q49" s="8">
-        <v>177</v>
+        <v>186.4</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B50" s="7">
-        <v>21.47</v>
+        <v>20.79</v>
       </c>
       <c r="C50" s="7">
-        <v>20.79</v>
+        <v>20.3</v>
       </c>
       <c r="D50" s="7">
-        <v>21.3</v>
+        <v>21.19</v>
       </c>
       <c r="E50" s="7">
-        <v>19.5</v>
+        <v>19.420000000000002</v>
       </c>
       <c r="F50" s="10">
-        <v>-0.68</v>
+        <v>-0.49</v>
       </c>
       <c r="G50" s="10">
-        <v>-3.17</v>
+        <v>-2.36</v>
       </c>
       <c r="H50" s="9">
-        <v>1.49</v>
-      </c>
-      <c r="I50" s="8">
-        <v>8102.6</v>
-      </c>
-      <c r="J50" s="8">
-        <v>51802.400000000001</v>
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="I50" s="10">
+        <v>-42.6</v>
+      </c>
+      <c r="J50" s="10">
+        <v>-85.1</v>
       </c>
       <c r="K50" s="9">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="L50" s="8">
-        <v>306.39999999999998</v>
+        <v>177</v>
       </c>
       <c r="M50" s="9">
-        <v>1.49</v>
-      </c>
-      <c r="N50" s="8">
-        <v>8102.6</v>
-      </c>
-      <c r="O50" s="8">
-        <v>51802.400000000001</v>
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="N50" s="10">
+        <v>-42.6</v>
+      </c>
+      <c r="O50" s="10">
+        <v>-85.1</v>
       </c>
       <c r="P50" s="9">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q50" s="8">
-        <v>306.39999999999998</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B51" s="7">
-        <v>21.91</v>
+        <v>21.47</v>
       </c>
       <c r="C51" s="7">
-        <v>21.47</v>
+        <v>20.79</v>
       </c>
       <c r="D51" s="7">
-        <v>24.51</v>
+        <v>21.3</v>
       </c>
       <c r="E51" s="7">
-        <v>21.01</v>
+        <v>19.5</v>
       </c>
       <c r="F51" s="10">
-        <v>-0.44</v>
+        <v>-0.68</v>
       </c>
       <c r="G51" s="10">
-        <v>-2.0099999999999998</v>
+        <v>-3.17</v>
       </c>
       <c r="H51" s="9">
-        <v>1.8200000000000001E-2</v>
+        <v>1.49</v>
       </c>
       <c r="I51" s="8">
-        <v>211.5</v>
-      </c>
-      <c r="J51" s="10">
-        <v>-93.7</v>
+        <v>8102.6</v>
+      </c>
+      <c r="J51" s="8">
+        <v>51802.400000000001</v>
       </c>
       <c r="K51" s="9">
-        <v>8.9499999999999996E-2</v>
-      </c>
-      <c r="L51" s="10">
-        <v>-76.8</v>
+        <v>1.58</v>
+      </c>
+      <c r="L51" s="8">
+        <v>306.39999999999998</v>
       </c>
       <c r="M51" s="9">
-        <v>1.8200000000000001E-2</v>
+        <v>1.49</v>
       </c>
       <c r="N51" s="8">
-        <v>211.5</v>
-      </c>
-      <c r="O51" s="10">
-        <v>-93.7</v>
+        <v>8102.6</v>
+      </c>
+      <c r="O51" s="8">
+        <v>51802.400000000001</v>
       </c>
       <c r="P51" s="9">
-        <v>8.9499999999999996E-2</v>
-      </c>
-      <c r="Q51" s="10">
-        <v>-76.8</v>
+        <v>1.58</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>306.39999999999998</v>
       </c>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B52" s="7">
-        <v>22.6</v>
+        <v>21.91</v>
       </c>
       <c r="C52" s="7">
-        <v>21.91</v>
+        <v>21.47</v>
       </c>
       <c r="D52" s="7">
-        <v>23.09</v>
+        <v>24.51</v>
       </c>
       <c r="E52" s="7">
-        <v>20.8</v>
+        <v>21.01</v>
       </c>
       <c r="F52" s="10">
-        <v>-0.69</v>
+        <v>-0.44</v>
       </c>
       <c r="G52" s="10">
-        <v>-3.05</v>
+        <v>-2.0099999999999998</v>
       </c>
       <c r="H52" s="9">
-        <v>5.7999999999999996E-3</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="I52" s="8">
-        <v>56.3</v>
-      </c>
-      <c r="J52" s="8">
-        <v>12.3</v>
+        <v>211.5</v>
+      </c>
+      <c r="J52" s="10">
+        <v>-93.7</v>
       </c>
       <c r="K52" s="9">
-        <v>7.1300000000000002E-2</v>
+        <v>8.9499999999999996E-2</v>
       </c>
       <c r="L52" s="10">
-        <v>-25.1</v>
+        <v>-76.8</v>
       </c>
       <c r="M52" s="9">
-        <v>5.7999999999999996E-3</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="N52" s="8">
-        <v>56.3</v>
-      </c>
-      <c r="O52" s="8">
-        <v>12.3</v>
+        <v>211.5</v>
+      </c>
+      <c r="O52" s="10">
+        <v>-93.7</v>
       </c>
       <c r="P52" s="9">
-        <v>7.1300000000000002E-2</v>
+        <v>8.9499999999999996E-2</v>
       </c>
       <c r="Q52" s="10">
-        <v>-25.1</v>
+        <v>-76.8</v>
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B53" s="7">
-        <v>24</v>
+        <v>22.6</v>
       </c>
       <c r="C53" s="7">
-        <v>22.6</v>
+        <v>21.91</v>
       </c>
       <c r="D53" s="7">
-        <v>24.7</v>
+        <v>23.09</v>
       </c>
       <c r="E53" s="7">
-        <v>21.51</v>
+        <v>20.8</v>
       </c>
       <c r="F53" s="10">
-        <v>-1.4</v>
+        <v>-0.69</v>
       </c>
       <c r="G53" s="10">
-        <v>-5.83</v>
+        <v>-3.05</v>
       </c>
       <c r="H53" s="9">
-        <v>3.7000000000000002E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="I53" s="8">
-        <v>107.2</v>
-      </c>
-      <c r="J53" s="10">
-        <v>-25.7</v>
+        <v>56.3</v>
+      </c>
+      <c r="J53" s="8">
+        <v>12.3</v>
       </c>
       <c r="K53" s="9">
-        <v>6.5500000000000003E-2</v>
+        <v>7.1300000000000002E-2</v>
       </c>
       <c r="L53" s="10">
-        <v>-27.2</v>
+        <v>-25.1</v>
       </c>
       <c r="M53" s="9">
-        <v>3.7000000000000002E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="N53" s="8">
-        <v>107.2</v>
-      </c>
-      <c r="O53" s="10">
-        <v>-25.7</v>
+        <v>56.3</v>
+      </c>
+      <c r="O53" s="8">
+        <v>12.3</v>
       </c>
       <c r="P53" s="9">
-        <v>6.5500000000000003E-2</v>
+        <v>7.1300000000000002E-2</v>
       </c>
       <c r="Q53" s="10">
-        <v>-27.2</v>
+        <v>-25.1</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B54" s="7">
-        <v>23.4</v>
+        <v>24</v>
       </c>
       <c r="C54" s="7">
-        <v>24</v>
+        <v>22.6</v>
       </c>
       <c r="D54" s="7">
-        <v>26.29</v>
+        <v>24.7</v>
       </c>
       <c r="E54" s="7">
-        <v>23.5</v>
-      </c>
-      <c r="F54" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="G54" s="8">
-        <v>2.56</v>
+        <v>21.51</v>
+      </c>
+      <c r="F54" s="10">
+        <v>-1.4</v>
+      </c>
+      <c r="G54" s="10">
+        <v>-5.83</v>
       </c>
       <c r="H54" s="9">
-        <v>1.8E-3</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="I54" s="8">
-        <v>27.6</v>
+        <v>107.2</v>
       </c>
       <c r="J54" s="10">
-        <v>-96.5</v>
+        <v>-25.7</v>
       </c>
       <c r="K54" s="9">
-        <v>6.1800000000000001E-2</v>
+        <v>6.5500000000000003E-2</v>
       </c>
       <c r="L54" s="10">
-        <v>-27.3</v>
+        <v>-27.2</v>
       </c>
       <c r="M54" s="9">
-        <v>1.8E-3</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="N54" s="8">
-        <v>27.6</v>
+        <v>107.2</v>
       </c>
       <c r="O54" s="10">
-        <v>-96.5</v>
+        <v>-25.7</v>
       </c>
       <c r="P54" s="9">
-        <v>6.1800000000000001E-2</v>
+        <v>6.5500000000000003E-2</v>
       </c>
       <c r="Q54" s="10">
-        <v>-27.3</v>
+        <v>-27.2</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B55" s="7">
-        <v>20.010000000000002</v>
+        <v>23.4</v>
       </c>
       <c r="C55" s="7">
-        <v>23.4</v>
+        <v>24</v>
       </c>
       <c r="D55" s="7">
-        <v>27.37</v>
+        <v>26.29</v>
       </c>
       <c r="E55" s="7">
-        <v>19.91</v>
+        <v>23.5</v>
       </c>
       <c r="F55" s="8">
-        <v>3.39</v>
+        <v>0.6</v>
       </c>
       <c r="G55" s="8">
-        <v>16.940000000000001</v>
+        <v>2.56</v>
       </c>
       <c r="H55" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="I55" s="10">
-        <v>-97.3</v>
+        <v>1.8E-3</v>
+      </c>
+      <c r="I55" s="8">
+        <v>27.6</v>
       </c>
       <c r="J55" s="10">
-        <v>-68</v>
+        <v>-96.5</v>
       </c>
       <c r="K55" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="L55" s="8">
-        <v>76.3</v>
+        <v>6.1800000000000001E-2</v>
+      </c>
+      <c r="L55" s="10">
+        <v>-27.3</v>
       </c>
       <c r="M55" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="N55" s="10">
-        <v>-97.3</v>
+        <v>1.8E-3</v>
+      </c>
+      <c r="N55" s="8">
+        <v>27.6</v>
       </c>
       <c r="O55" s="10">
-        <v>-68</v>
+        <v>-96.5</v>
       </c>
       <c r="P55" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="Q55" s="8">
-        <v>76.3</v>
+        <v>6.1800000000000001E-2</v>
+      </c>
+      <c r="Q55" s="10">
+        <v>-27.3</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B56" s="7">
-        <v>24</v>
+        <v>20.010000000000002</v>
       </c>
       <c r="C56" s="7">
-        <v>20.010000000000002</v>
+        <v>23.4</v>
       </c>
       <c r="D56" s="7">
-        <v>24.5</v>
+        <v>27.37</v>
       </c>
       <c r="E56" s="7">
-        <v>18.940000000000001</v>
-      </c>
-      <c r="F56" s="10">
-        <v>-3.99</v>
-      </c>
-      <c r="G56" s="10">
-        <v>-16.62</v>
+        <v>19.91</v>
+      </c>
+      <c r="F56" s="8">
+        <v>3.39</v>
+      </c>
+      <c r="G56" s="8">
+        <v>16.940000000000001</v>
       </c>
       <c r="H56" s="9">
-        <v>5.2299999999999999E-2</v>
-      </c>
-      <c r="I56" s="8">
-        <v>3635</v>
-      </c>
-      <c r="J56" s="8">
-        <v>3608.5</v>
+        <v>1.4E-3</v>
+      </c>
+      <c r="I56" s="10">
+        <v>-97.3</v>
+      </c>
+      <c r="J56" s="10">
+        <v>-68</v>
       </c>
       <c r="K56" s="9">
-        <v>5.8599999999999999E-2</v>
+        <v>0.06</v>
       </c>
       <c r="L56" s="8">
-        <v>97.8</v>
+        <v>76.3</v>
       </c>
       <c r="M56" s="9">
-        <v>5.2299999999999999E-2</v>
-      </c>
-      <c r="N56" s="8">
-        <v>3635</v>
-      </c>
-      <c r="O56" s="8">
-        <v>3608.5</v>
+        <v>1.4E-3</v>
+      </c>
+      <c r="N56" s="10">
+        <v>-97.3</v>
+      </c>
+      <c r="O56" s="10">
+        <v>-68</v>
       </c>
       <c r="P56" s="9">
-        <v>5.8599999999999999E-2</v>
+        <v>0.06</v>
       </c>
       <c r="Q56" s="8">
-        <v>97.8</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B57" s="7">
-        <v>15.95</v>
+        <v>24</v>
       </c>
       <c r="C57" s="7">
-        <v>24</v>
+        <v>20.010000000000002</v>
       </c>
       <c r="D57" s="7">
-        <v>25.1</v>
+        <v>24.5</v>
       </c>
       <c r="E57" s="7">
-        <v>14.88</v>
-      </c>
-      <c r="F57" s="8">
-        <v>8.0500000000000007</v>
-      </c>
-      <c r="G57" s="8">
-        <v>50.47</v>
+        <v>18.940000000000001</v>
+      </c>
+      <c r="F57" s="10">
+        <v>-3.99</v>
+      </c>
+      <c r="G57" s="10">
+        <v>-16.62</v>
       </c>
       <c r="H57" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="I57" s="10">
-        <v>-56.2</v>
-      </c>
-      <c r="J57" s="10">
-        <v>-17.2</v>
+        <v>5.2299999999999999E-2</v>
+      </c>
+      <c r="I57" s="8">
+        <v>3635</v>
+      </c>
+      <c r="J57" s="8">
+        <v>3608.5</v>
       </c>
       <c r="K57" s="9">
-        <v>6.3E-3</v>
-      </c>
-      <c r="L57" s="10">
-        <v>-77.8</v>
+        <v>5.8599999999999999E-2</v>
+      </c>
+      <c r="L57" s="8">
+        <v>97.8</v>
       </c>
       <c r="M57" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="N57" s="10">
-        <v>-56.2</v>
-      </c>
-      <c r="O57" s="10">
-        <v>-17.2</v>
+        <v>5.2299999999999999E-2</v>
+      </c>
+      <c r="N57" s="8">
+        <v>3635</v>
+      </c>
+      <c r="O57" s="8">
+        <v>3608.5</v>
       </c>
       <c r="P57" s="9">
-        <v>6.3E-3</v>
-      </c>
-      <c r="Q57" s="10">
-        <v>-77.8</v>
+        <v>5.8599999999999999E-2</v>
+      </c>
+      <c r="Q57" s="8">
+        <v>97.8</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B58" s="7">
-        <v>16</v>
+        <v>15.95</v>
       </c>
       <c r="C58" s="7">
-        <v>15.95</v>
+        <v>24</v>
       </c>
       <c r="D58" s="7">
-        <v>16.190000000000001</v>
+        <v>25.1</v>
       </c>
       <c r="E58" s="7">
-        <v>14.81</v>
-      </c>
-      <c r="F58" s="10">
-        <v>-0.05</v>
-      </c>
-      <c r="G58" s="10">
-        <v>-0.31</v>
+        <v>14.88</v>
+      </c>
+      <c r="F58" s="8">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="G58" s="8">
+        <v>50.47</v>
       </c>
       <c r="H58" s="9">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="I58" s="8">
-        <v>91.6</v>
+        <v>1.4E-3</v>
+      </c>
+      <c r="I58" s="10">
+        <v>-56.2</v>
       </c>
       <c r="J58" s="10">
-        <v>-87.1</v>
+        <v>-17.2</v>
       </c>
       <c r="K58" s="9">
-        <v>4.8999999999999998E-3</v>
+        <v>6.3E-3</v>
       </c>
       <c r="L58" s="10">
-        <v>-81.599999999999994</v>
+        <v>-77.8</v>
       </c>
       <c r="M58" s="9">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="N58" s="8">
-        <v>91.6</v>
+        <v>1.4E-3</v>
+      </c>
+      <c r="N58" s="10">
+        <v>-56.2</v>
       </c>
       <c r="O58" s="10">
-        <v>-87.1</v>
+        <v>-17.2</v>
       </c>
       <c r="P58" s="9">
-        <v>4.8999999999999998E-3</v>
+        <v>6.3E-3</v>
       </c>
       <c r="Q58" s="10">
-        <v>-81.599999999999994</v>
+        <v>-77.8</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B59" s="7">
-        <v>16.29</v>
+        <v>16</v>
       </c>
       <c r="C59" s="7">
-        <v>16</v>
+        <v>15.95</v>
       </c>
       <c r="D59" s="7">
-        <v>16.79</v>
+        <v>16.190000000000001</v>
       </c>
       <c r="E59" s="7">
-        <v>15.51</v>
+        <v>14.81</v>
       </c>
       <c r="F59" s="10">
-        <v>-0.28999999999999998</v>
+        <v>-0.05</v>
       </c>
       <c r="G59" s="10">
-        <v>-1.78</v>
+        <v>-0.31</v>
       </c>
       <c r="H59" s="9">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="I59" s="10">
-        <v>-86.4</v>
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="I59" s="8">
+        <v>91.6</v>
       </c>
       <c r="J59" s="10">
-        <v>-5.1100000000000003</v>
+        <v>-87.1</v>
       </c>
       <c r="K59" s="9">
-        <v>1.6999999999999999E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="L59" s="10">
-        <v>-5.1100000000000003</v>
+        <v>-81.599999999999994</v>
       </c>
       <c r="M59" s="9">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="N59" s="10">
-        <v>-86.4</v>
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="N59" s="8">
+        <v>91.6</v>
       </c>
       <c r="O59" s="10">
-        <v>-5.1100000000000003</v>
+        <v>-87.1</v>
       </c>
       <c r="P59" s="9">
-        <v>1.6999999999999999E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="Q59" s="10">
-        <v>-5.1100000000000003</v>
+        <v>-81.599999999999994</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B60" s="7">
-        <v>14.04</v>
+        <v>16.29</v>
       </c>
       <c r="C60" s="7">
-        <v>16.29</v>
+        <v>16</v>
       </c>
       <c r="D60" s="7">
-        <v>16.55</v>
+        <v>16.79</v>
       </c>
       <c r="E60" s="7">
-        <v>14</v>
-      </c>
-      <c r="F60" s="8">
-        <v>2.25</v>
-      </c>
-      <c r="G60" s="8">
-        <v>16.03</v>
+        <v>15.51</v>
+      </c>
+      <c r="F60" s="10">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="G60" s="10">
+        <v>-1.78</v>
       </c>
       <c r="H60" s="9">
-        <v>1.23E-2</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="I60" s="10">
-        <v>-93.6</v>
-      </c>
-      <c r="J60" s="8">
-        <v>113.6</v>
+        <v>-86.4</v>
+      </c>
+      <c r="J60" s="10">
+        <v>-5.1100000000000003</v>
       </c>
       <c r="K60" s="9">
-        <v>0.59299999999999997</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="L60" s="10">
-        <v>-29.6</v>
+        <v>-5.1100000000000003</v>
       </c>
       <c r="M60" s="9">
-        <v>1.23E-2</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="N60" s="10">
-        <v>-93.6</v>
-      </c>
-      <c r="O60" s="8">
-        <v>113.6</v>
+        <v>-86.4</v>
+      </c>
+      <c r="O60" s="10">
+        <v>-5.1100000000000003</v>
       </c>
       <c r="P60" s="9">
-        <v>0.59299999999999997</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="Q60" s="10">
-        <v>-29.6</v>
+        <v>-5.1100000000000003</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B61" s="7">
-        <v>13.99</v>
+        <v>14.04</v>
       </c>
       <c r="C61" s="7">
-        <v>14.04</v>
+        <v>16.29</v>
       </c>
       <c r="D61" s="7">
-        <v>15.13</v>
+        <v>16.55</v>
       </c>
       <c r="E61" s="7">
-        <v>12.3</v>
+        <v>14</v>
       </c>
       <c r="F61" s="8">
-        <v>0.05</v>
+        <v>2.25</v>
       </c>
       <c r="G61" s="8">
-        <v>0.36</v>
+        <v>16.03</v>
       </c>
       <c r="H61" s="9">
-        <v>0.192</v>
-      </c>
-      <c r="I61" s="8">
-        <v>6584.7</v>
+        <v>1.23E-2</v>
+      </c>
+      <c r="I61" s="10">
+        <v>-93.6</v>
       </c>
       <c r="J61" s="8">
-        <v>5289</v>
+        <v>113.6</v>
       </c>
       <c r="K61" s="9">
-        <v>0.57999999999999996</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="L61" s="10">
-        <v>-30.6</v>
+        <v>-29.6</v>
       </c>
       <c r="M61" s="9">
-        <v>0.192</v>
-      </c>
-      <c r="N61" s="8">
-        <v>6584.7</v>
+        <v>1.23E-2</v>
+      </c>
+      <c r="N61" s="10">
+        <v>-93.6</v>
       </c>
       <c r="O61" s="8">
-        <v>5289</v>
+        <v>113.6</v>
       </c>
       <c r="P61" s="9">
-        <v>0.57999999999999996</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="Q61" s="10">
-        <v>-30.6</v>
+        <v>-29.6</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B62" s="7">
-        <v>13.14</v>
+        <v>13.99</v>
       </c>
       <c r="C62" s="7">
-        <v>13.99</v>
+        <v>14.04</v>
       </c>
       <c r="D62" s="7">
-        <v>15.23</v>
+        <v>15.13</v>
       </c>
       <c r="E62" s="7">
-        <v>13.15</v>
+        <v>12.3</v>
       </c>
       <c r="F62" s="8">
-        <v>0.85</v>
+        <v>0.05</v>
       </c>
       <c r="G62" s="8">
-        <v>6.47</v>
+        <v>0.36</v>
       </c>
       <c r="H62" s="9">
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="I62" s="10">
-        <v>-99</v>
-      </c>
-      <c r="J62" s="10">
-        <v>-33.4</v>
+        <v>0.192</v>
+      </c>
+      <c r="I62" s="8">
+        <v>6584.7</v>
+      </c>
+      <c r="J62" s="8">
+        <v>5289</v>
       </c>
       <c r="K62" s="9">
-        <v>0.38900000000000001</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L62" s="10">
-        <v>-53.3</v>
+        <v>-30.6</v>
       </c>
       <c r="M62" s="9">
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="N62" s="10">
-        <v>-99</v>
-      </c>
-      <c r="O62" s="10">
-        <v>-33.4</v>
+        <v>0.192</v>
+      </c>
+      <c r="N62" s="8">
+        <v>6584.7</v>
+      </c>
+      <c r="O62" s="8">
+        <v>5289</v>
       </c>
       <c r="P62" s="9">
-        <v>0.38900000000000001</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="Q62" s="10">
-        <v>-53.3</v>
+        <v>-30.6</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B63" s="7">
-        <v>11.61</v>
+        <v>13.14</v>
       </c>
       <c r="C63" s="7">
-        <v>13.14</v>
+        <v>13.99</v>
       </c>
       <c r="D63" s="7">
-        <v>16.09</v>
+        <v>15.23</v>
       </c>
       <c r="E63" s="7">
-        <v>11.31</v>
+        <v>13.15</v>
       </c>
       <c r="F63" s="8">
-        <v>1.53</v>
+        <v>0.85</v>
       </c>
       <c r="G63" s="8">
-        <v>13.18</v>
+        <v>6.47</v>
       </c>
       <c r="H63" s="9">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="I63" s="8">
-        <v>5496.7</v>
-      </c>
-      <c r="J63" s="8">
-        <v>17398.2</v>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="I63" s="10">
+        <v>-99</v>
+      </c>
+      <c r="J63" s="10">
+        <v>-33.4</v>
       </c>
       <c r="K63" s="9">
-        <v>0.38600000000000001</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="L63" s="10">
-        <v>-53.4</v>
+        <v>-53.3</v>
       </c>
       <c r="M63" s="9">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="N63" s="8">
-        <v>5496.7</v>
-      </c>
-      <c r="O63" s="8">
-        <v>17398.2</v>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="N63" s="10">
+        <v>-99</v>
+      </c>
+      <c r="O63" s="10">
+        <v>-33.4</v>
       </c>
       <c r="P63" s="9">
-        <v>0.38600000000000001</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="Q63" s="10">
-        <v>-53.4</v>
+        <v>-53.3</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B64" s="7">
-        <v>12.8</v>
+        <v>11.61</v>
       </c>
       <c r="C64" s="7">
-        <v>11.61</v>
+        <v>13.14</v>
       </c>
       <c r="D64" s="7">
-        <v>13.05</v>
+        <v>16.09</v>
       </c>
       <c r="E64" s="7">
         <v>11.31</v>
       </c>
-      <c r="F64" s="10">
-        <v>-1.19</v>
-      </c>
-      <c r="G64" s="10">
-        <v>-9.3000000000000007</v>
+      <c r="F64" s="8">
+        <v>1.53</v>
+      </c>
+      <c r="G64" s="8">
+        <v>13.18</v>
       </c>
       <c r="H64" s="9">
-        <v>5.1999999999999998E-3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I64" s="8">
-        <v>3.38</v>
+        <v>5496.7</v>
       </c>
       <c r="J64" s="8">
-        <v>92.2</v>
+        <v>17398.2</v>
       </c>
       <c r="K64" s="9">
-        <v>9.5200000000000007E-2</v>
+        <v>0.38600000000000001</v>
       </c>
       <c r="L64" s="10">
-        <v>-88.5</v>
+        <v>-53.4</v>
       </c>
       <c r="M64" s="9">
-        <v>5.1999999999999998E-3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="N64" s="8">
-        <v>3.38</v>
+        <v>5496.7</v>
       </c>
       <c r="O64" s="8">
-        <v>92.2</v>
+        <v>17398.2</v>
       </c>
       <c r="P64" s="9">
-        <v>9.5200000000000007E-2</v>
+        <v>0.38600000000000001</v>
       </c>
       <c r="Q64" s="10">
-        <v>-88.5</v>
+        <v>-53.4</v>
       </c>
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B65" s="7">
-        <v>14</v>
+        <v>12.8</v>
       </c>
       <c r="C65" s="7">
-        <v>12.8</v>
+        <v>11.61</v>
       </c>
       <c r="D65" s="7">
-        <v>14.76</v>
+        <v>13.05</v>
       </c>
       <c r="E65" s="7">
-        <v>12.54</v>
+        <v>11.31</v>
       </c>
       <c r="F65" s="10">
-        <v>-1.2</v>
+        <v>-1.19</v>
       </c>
       <c r="G65" s="10">
-        <v>-8.57</v>
+        <v>-9.3000000000000007</v>
       </c>
       <c r="H65" s="9">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="I65" s="10">
-        <v>-90.2</v>
-      </c>
-      <c r="J65" s="10">
-        <v>-7.2</v>
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="I65" s="8">
+        <v>3.38</v>
+      </c>
+      <c r="J65" s="8">
+        <v>92.2</v>
       </c>
       <c r="K65" s="9">
-        <v>0.09</v>
+        <v>9.5200000000000007E-2</v>
       </c>
       <c r="L65" s="10">
-        <v>-89.1</v>
+        <v>-88.5</v>
       </c>
       <c r="M65" s="9">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="N65" s="10">
-        <v>-90.2</v>
-      </c>
-      <c r="O65" s="10">
-        <v>-7.2</v>
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="N65" s="8">
+        <v>3.38</v>
+      </c>
+      <c r="O65" s="8">
+        <v>92.2</v>
       </c>
       <c r="P65" s="9">
-        <v>0.09</v>
+        <v>9.5200000000000007E-2</v>
       </c>
       <c r="Q65" s="10">
-        <v>-89.1</v>
+        <v>-88.5</v>
       </c>
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B66" s="7">
-        <v>12.2</v>
+        <v>14</v>
       </c>
       <c r="C66" s="7">
-        <v>14</v>
+        <v>12.8</v>
       </c>
       <c r="D66" s="7">
-        <v>16.52</v>
+        <v>14.76</v>
       </c>
       <c r="E66" s="7">
-        <v>12</v>
-      </c>
-      <c r="F66" s="8">
-        <v>1.8</v>
-      </c>
-      <c r="G66" s="8">
-        <v>14.75</v>
+        <v>12.54</v>
+      </c>
+      <c r="F66" s="10">
+        <v>-1.2</v>
+      </c>
+      <c r="G66" s="10">
+        <v>-8.57</v>
       </c>
       <c r="H66" s="9">
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="I66" s="8">
-        <v>1059.3</v>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I66" s="10">
+        <v>-90.2</v>
       </c>
       <c r="J66" s="10">
-        <v>-72.599999999999994</v>
+        <v>-7.2</v>
       </c>
       <c r="K66" s="9">
-        <v>8.5000000000000006E-2</v>
+        <v>0.09</v>
       </c>
       <c r="L66" s="10">
-        <v>-89.6</v>
+        <v>-89.1</v>
       </c>
       <c r="M66" s="9">
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="N66" s="8">
-        <v>1059.3</v>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="N66" s="10">
+        <v>-90.2</v>
       </c>
       <c r="O66" s="10">
-        <v>-72.599999999999994</v>
+        <v>-7.2</v>
       </c>
       <c r="P66" s="9">
-        <v>8.5000000000000006E-2</v>
+        <v>0.09</v>
       </c>
       <c r="Q66" s="10">
-        <v>-89.6</v>
+        <v>-89.1</v>
       </c>
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B67" s="7">
-        <v>12.15</v>
+        <v>12.2</v>
       </c>
       <c r="C67" s="7">
-        <v>12.2</v>
+        <v>14</v>
       </c>
       <c r="D67" s="7">
-        <v>12.78</v>
+        <v>16.52</v>
       </c>
       <c r="E67" s="7">
-        <v>11.2</v>
+        <v>12</v>
       </c>
       <c r="F67" s="8">
-        <v>0.05</v>
+        <v>1.8</v>
       </c>
       <c r="G67" s="8">
-        <v>0.41</v>
+        <v>14.75</v>
       </c>
       <c r="H67" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="I67" s="8">
-        <v>212</v>
-      </c>
-      <c r="J67" s="8">
-        <v>1089.2</v>
+        <v>1059.3</v>
+      </c>
+      <c r="J67" s="10">
+        <v>-72.599999999999994</v>
       </c>
       <c r="K67" s="9">
-        <v>3.4000000000000002E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="L67" s="10">
-        <v>-94.6</v>
+        <v>-89.6</v>
       </c>
       <c r="M67" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="N67" s="8">
-        <v>212</v>
-      </c>
-      <c r="O67" s="8">
-        <v>1089.2</v>
+        <v>1059.3</v>
+      </c>
+      <c r="O67" s="10">
+        <v>-72.599999999999994</v>
       </c>
       <c r="P67" s="9">
-        <v>3.4000000000000002E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="Q67" s="10">
-        <v>-94.6</v>
+        <v>-89.6</v>
       </c>
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B68" s="7">
-        <v>10.52</v>
+        <v>12.15</v>
       </c>
       <c r="C68" s="7">
-        <v>12.15</v>
+        <v>12.2</v>
       </c>
       <c r="D68" s="7">
-        <v>15.7</v>
+        <v>12.78</v>
       </c>
       <c r="E68" s="7">
-        <v>10.01</v>
+        <v>11.2</v>
       </c>
       <c r="F68" s="8">
-        <v>1.63</v>
+        <v>0.05</v>
       </c>
       <c r="G68" s="8">
-        <v>15.49</v>
+        <v>0.41</v>
       </c>
       <c r="H68" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="I68" s="10">
-        <v>-16.600000000000001</v>
-      </c>
-      <c r="J68" s="10">
-        <v>-99.8</v>
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="I68" s="8">
+        <v>212</v>
+      </c>
+      <c r="J68" s="8">
+        <v>1089.2</v>
       </c>
       <c r="K68" s="9">
-        <v>2.9600000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="L68" s="10">
-        <v>-95.3</v>
+        <v>-94.6</v>
       </c>
       <c r="M68" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="N68" s="10">
-        <v>-16.600000000000001</v>
-      </c>
-      <c r="O68" s="10">
-        <v>-99.8</v>
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="N68" s="8">
+        <v>212</v>
+      </c>
+      <c r="O68" s="8">
+        <v>1089.2</v>
       </c>
       <c r="P68" s="9">
-        <v>2.9600000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="Q68" s="10">
-        <v>-95.3</v>
+        <v>-94.6</v>
       </c>
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B69" s="7">
-        <v>11.74</v>
+        <v>10.52</v>
       </c>
       <c r="C69" s="7">
-        <v>10.52</v>
+        <v>12.15</v>
       </c>
       <c r="D69" s="7">
-        <v>12.34</v>
+        <v>15.7</v>
       </c>
       <c r="E69" s="7">
-        <v>10</v>
-      </c>
-      <c r="F69" s="10">
-        <v>-1.22</v>
-      </c>
-      <c r="G69" s="10">
-        <v>-10.39</v>
+        <v>10.01</v>
+      </c>
+      <c r="F69" s="8">
+        <v>1.63</v>
+      </c>
+      <c r="G69" s="8">
+        <v>15.49</v>
       </c>
       <c r="H69" s="9">
-        <v>1.6999999999999999E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="I69" s="10">
-        <v>-93.2</v>
-      </c>
-      <c r="J69" s="8">
-        <v>22.5</v>
+        <v>-16.600000000000001</v>
+      </c>
+      <c r="J69" s="10">
+        <v>-99.8</v>
       </c>
       <c r="K69" s="9">
-        <v>2.8199999999999999E-2</v>
-      </c>
-      <c r="L69" s="8">
-        <v>389.6</v>
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="L69" s="10">
+        <v>-95.3</v>
       </c>
       <c r="M69" s="9">
-        <v>1.6999999999999999E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="N69" s="10">
-        <v>-93.2</v>
-      </c>
-      <c r="O69" s="8">
-        <v>22.5</v>
+        <v>-16.600000000000001</v>
+      </c>
+      <c r="O69" s="10">
+        <v>-99.8</v>
       </c>
       <c r="P69" s="9">
-        <v>2.8199999999999999E-2</v>
-      </c>
-      <c r="Q69" s="8">
-        <v>389.6</v>
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="Q69" s="10">
+        <v>-95.3</v>
       </c>
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B70" s="7">
-        <v>11.91</v>
+        <v>11.74</v>
       </c>
       <c r="C70" s="7">
-        <v>11.74</v>
+        <v>10.52</v>
       </c>
       <c r="D70" s="7">
-        <v>12.72</v>
+        <v>12.34</v>
       </c>
       <c r="E70" s="7">
-        <v>10.41</v>
+        <v>10</v>
       </c>
       <c r="F70" s="10">
-        <v>-0.17</v>
+        <v>-1.22</v>
       </c>
       <c r="G70" s="10">
-        <v>-1.43</v>
+        <v>-10.39</v>
       </c>
       <c r="H70" s="9">
-        <v>2.4799999999999999E-2</v>
-      </c>
-      <c r="I70" s="8">
-        <v>1306.2</v>
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="I70" s="10">
+        <v>-93.2</v>
       </c>
       <c r="J70" s="8">
-        <v>1137.5</v>
+        <v>22.5</v>
       </c>
       <c r="K70" s="9">
-        <v>2.6499999999999999E-2</v>
+        <v>2.8199999999999999E-2</v>
       </c>
       <c r="L70" s="8">
-        <v>505.2</v>
+        <v>389.6</v>
       </c>
       <c r="M70" s="9">
-        <v>2.4799999999999999E-2</v>
-      </c>
-      <c r="N70" s="8">
-        <v>1306.2</v>
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="N70" s="10">
+        <v>-93.2</v>
       </c>
       <c r="O70" s="8">
-        <v>1137.5</v>
+        <v>22.5</v>
       </c>
       <c r="P70" s="9">
-        <v>2.6499999999999999E-2</v>
+        <v>2.8199999999999999E-2</v>
       </c>
       <c r="Q70" s="8">
-        <v>505.2</v>
+        <v>389.6</v>
       </c>
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42736</v>
+        <v>42767</v>
       </c>
       <c r="B71" s="7">
-        <v>13.39</v>
+        <v>11.91</v>
       </c>
       <c r="C71" s="7">
-        <v>11.91</v>
+        <v>11.74</v>
       </c>
       <c r="D71" s="7">
-        <v>12.99</v>
+        <v>12.72</v>
       </c>
       <c r="E71" s="7">
-        <v>11.3</v>
+        <v>10.41</v>
       </c>
       <c r="F71" s="10">
-        <v>-1.48</v>
+        <v>-0.17</v>
       </c>
       <c r="G71" s="10">
-        <v>-11.05</v>
+        <v>-1.43</v>
       </c>
       <c r="H71" s="9">
-        <v>1.8E-3</v>
-      </c>
-      <c r="I71" s="10">
-        <v>-69.3</v>
-      </c>
-      <c r="J71" s="10">
-        <v>-26</v>
+        <v>2.4799999999999999E-2</v>
+      </c>
+      <c r="I71" s="8">
+        <v>1306.2</v>
+      </c>
+      <c r="J71" s="8">
+        <v>1137.5</v>
       </c>
       <c r="K71" s="9">
-        <v>1.8E-3</v>
-      </c>
-      <c r="L71" s="10">
-        <v>-26</v>
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="L71" s="8">
+        <v>505.2</v>
       </c>
       <c r="M71" s="9">
-        <v>1.8E-3</v>
-      </c>
-      <c r="N71" s="10">
-        <v>-69.3</v>
-      </c>
-      <c r="O71" s="10">
-        <v>-26</v>
+        <v>2.4799999999999999E-2</v>
+      </c>
+      <c r="N71" s="8">
+        <v>1306.2</v>
+      </c>
+      <c r="O71" s="8">
+        <v>1137.5</v>
       </c>
       <c r="P71" s="9">
-        <v>1.8E-3</v>
-      </c>
-      <c r="Q71" s="10">
-        <v>-26</v>
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>505.2</v>
       </c>
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>42705</v>
+        <v>42736</v>
       </c>
       <c r="B72" s="7">
-        <v>11.99</v>
+        <v>13.39</v>
       </c>
       <c r="C72" s="7">
-        <v>13.39</v>
+        <v>11.91</v>
       </c>
       <c r="D72" s="7">
-        <v>14.56</v>
+        <v>12.99</v>
       </c>
       <c r="E72" s="7">
-        <v>10.97</v>
-      </c>
-      <c r="F72" s="8">
-        <v>1.4</v>
-      </c>
-      <c r="G72" s="8">
-        <v>11.68</v>
+        <v>11.3</v>
+      </c>
+      <c r="F72" s="10">
+        <v>-1.48</v>
+      </c>
+      <c r="G72" s="10">
+        <v>-11.05</v>
       </c>
       <c r="H72" s="9">
-        <v>5.7000000000000002E-3</v>
-      </c>
-      <c r="I72" s="8">
-        <v>61.2</v>
+        <v>1.8E-3</v>
+      </c>
+      <c r="I72" s="10">
+        <v>-69.3</v>
       </c>
       <c r="J72" s="10">
-        <v>-96.4</v>
+        <v>-26</v>
       </c>
       <c r="K72" s="9">
-        <v>0.84199999999999997</v>
+        <v>1.8E-3</v>
       </c>
       <c r="L72" s="10">
-        <v>-60.3</v>
+        <v>-26</v>
       </c>
       <c r="M72" s="9">
-        <v>5.7000000000000002E-3</v>
-      </c>
-      <c r="N72" s="8">
-        <v>61.2</v>
+        <v>1.8E-3</v>
+      </c>
+      <c r="N72" s="10">
+        <v>-69.3</v>
       </c>
       <c r="O72" s="10">
-        <v>-96.4</v>
+        <v>-26</v>
       </c>
       <c r="P72" s="9">
-        <v>0.84199999999999997</v>
+        <v>1.8E-3</v>
       </c>
       <c r="Q72" s="10">
-        <v>-60.3</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>42675</v>
+        <v>42705</v>
       </c>
       <c r="B73" s="7">
-        <v>14.09</v>
+        <v>11.99</v>
       </c>
       <c r="C73" s="7">
-        <v>11.99</v>
+        <v>13.39</v>
       </c>
       <c r="D73" s="7">
-        <v>13.88</v>
+        <v>14.56</v>
       </c>
       <c r="E73" s="7">
-        <v>11.51</v>
-      </c>
-      <c r="F73" s="10">
-        <v>-2.1</v>
-      </c>
-      <c r="G73" s="10">
-        <v>-14.9</v>
+        <v>10.97</v>
+      </c>
+      <c r="F73" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="G73" s="8">
+        <v>11.68</v>
       </c>
       <c r="H73" s="9">
-        <v>3.5999999999999999E-3</v>
-      </c>
-      <c r="I73" s="10">
-        <v>-17.399999999999999</v>
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="I73" s="8">
+        <v>61.2</v>
       </c>
       <c r="J73" s="10">
-        <v>-99.6</v>
+        <v>-96.4</v>
       </c>
       <c r="K73" s="9">
-        <v>0.83599999999999997</v>
+        <v>0.84199999999999997</v>
       </c>
       <c r="L73" s="10">
-        <v>-57.4</v>
+        <v>-60.3</v>
       </c>
       <c r="M73" s="9">
-        <v>3.5999999999999999E-3</v>
-      </c>
-      <c r="N73" s="10">
-        <v>-17.399999999999999</v>
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="N73" s="8">
+        <v>61.2</v>
       </c>
       <c r="O73" s="10">
-        <v>-99.6</v>
+        <v>-96.4</v>
       </c>
       <c r="P73" s="9">
-        <v>0.83599999999999997</v>
+        <v>0.84199999999999997</v>
       </c>
       <c r="Q73" s="10">
-        <v>-57.4</v>
+        <v>-60.3</v>
       </c>
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="B74" s="7">
-        <v>14.2</v>
+        <v>14.09</v>
       </c>
       <c r="C74" s="7">
-        <v>14.09</v>
+        <v>11.99</v>
       </c>
       <c r="D74" s="7">
-        <v>14.29</v>
+        <v>13.88</v>
       </c>
       <c r="E74" s="7">
-        <v>13</v>
+        <v>11.51</v>
       </c>
       <c r="F74" s="10">
-        <v>-0.11</v>
+        <v>-2.1</v>
       </c>
       <c r="G74" s="10">
-        <v>-0.77</v>
+        <v>-14.9</v>
       </c>
       <c r="H74" s="9">
-        <v>4.3E-3</v>
-      </c>
-      <c r="I74" s="8">
-        <v>159.6</v>
-      </c>
-      <c r="J74" s="8">
-        <v>193.2</v>
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="I74" s="10">
+        <v>-17.399999999999999</v>
+      </c>
+      <c r="J74" s="10">
+        <v>-99.6</v>
       </c>
       <c r="K74" s="9">
-        <v>0.83199999999999996</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="L74" s="10">
-        <v>-24.2</v>
+        <v>-57.4</v>
       </c>
       <c r="M74" s="9">
-        <v>4.3E-3</v>
-      </c>
-      <c r="N74" s="8">
-        <v>159.6</v>
-      </c>
-      <c r="O74" s="8">
-        <v>193.2</v>
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="N74" s="10">
+        <v>-17.399999999999999</v>
+      </c>
+      <c r="O74" s="10">
+        <v>-99.6</v>
       </c>
       <c r="P74" s="9">
-        <v>0.83199999999999996</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="Q74" s="10">
-        <v>-24.2</v>
+        <v>-57.4</v>
       </c>
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="B75" s="7">
-        <v>15.75</v>
+        <v>14.2</v>
       </c>
       <c r="C75" s="7">
-        <v>14.2</v>
+        <v>14.09</v>
       </c>
       <c r="D75" s="7">
-        <v>16.21</v>
+        <v>14.29</v>
       </c>
       <c r="E75" s="7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="F75" s="10">
-        <v>-1.55</v>
+        <v>-0.11</v>
       </c>
       <c r="G75" s="10">
-        <v>-9.84</v>
+        <v>-0.77</v>
       </c>
       <c r="H75" s="9">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="I75" s="10">
-        <v>-38.5</v>
+        <v>4.3E-3</v>
+      </c>
+      <c r="I75" s="8">
+        <v>159.6</v>
       </c>
       <c r="J75" s="8">
-        <v>186.2</v>
+        <v>193.2</v>
       </c>
       <c r="K75" s="9">
-        <v>0.82799999999999996</v>
+        <v>0.83199999999999996</v>
       </c>
       <c r="L75" s="10">
-        <v>-24.5</v>
+        <v>-24.2</v>
       </c>
       <c r="M75" s="9">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="N75" s="10">
-        <v>-38.5</v>
+        <v>4.3E-3</v>
+      </c>
+      <c r="N75" s="8">
+        <v>159.6</v>
       </c>
       <c r="O75" s="8">
-        <v>186.2</v>
+        <v>193.2</v>
       </c>
       <c r="P75" s="9">
-        <v>0.82799999999999996</v>
+        <v>0.83199999999999996</v>
       </c>
       <c r="Q75" s="10">
-        <v>-24.5</v>
+        <v>-24.2</v>
       </c>
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>42583</v>
+        <v>42614</v>
       </c>
       <c r="B76" s="7">
-        <v>18.41</v>
+        <v>15.75</v>
       </c>
       <c r="C76" s="7">
-        <v>15.75</v>
+        <v>14.2</v>
       </c>
       <c r="D76" s="7">
-        <v>18.420000000000002</v>
+        <v>16.21</v>
       </c>
       <c r="E76" s="7">
-        <v>10.050000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="F76" s="10">
-        <v>-2.66</v>
+        <v>-1.55</v>
       </c>
       <c r="G76" s="10">
-        <v>-14.45</v>
+        <v>-9.84</v>
       </c>
       <c r="H76" s="9">
-        <v>2.7000000000000001E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="I76" s="10">
-        <v>-50.1</v>
-      </c>
-      <c r="J76" s="10">
-        <v>-98.9</v>
+        <v>-38.5</v>
+      </c>
+      <c r="J76" s="8">
+        <v>186.2</v>
       </c>
       <c r="K76" s="9">
-        <v>0.82599999999999996</v>
+        <v>0.82799999999999996</v>
       </c>
       <c r="L76" s="10">
-        <v>-24.6</v>
+        <v>-24.5</v>
       </c>
       <c r="M76" s="9">
-        <v>2.7000000000000001E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="N76" s="10">
-        <v>-50.1</v>
-      </c>
-      <c r="O76" s="10">
-        <v>-98.9</v>
+        <v>-38.5</v>
+      </c>
+      <c r="O76" s="8">
+        <v>186.2</v>
       </c>
       <c r="P76" s="9">
-        <v>0.82599999999999996</v>
+        <v>0.82799999999999996</v>
       </c>
       <c r="Q76" s="10">
-        <v>-24.6</v>
+        <v>-24.5</v>
       </c>
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>42552</v>
+        <v>42583</v>
       </c>
       <c r="B77" s="7">
-        <v>19.39</v>
+        <v>18.41</v>
       </c>
       <c r="C77" s="7">
-        <v>18.41</v>
+        <v>15.75</v>
       </c>
       <c r="D77" s="7">
-        <v>19.7</v>
+        <v>18.420000000000002</v>
       </c>
       <c r="E77" s="7">
-        <v>17.579999999999998</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="F77" s="10">
-        <v>-0.98</v>
+        <v>-2.66</v>
       </c>
       <c r="G77" s="10">
-        <v>-5.05</v>
+        <v>-14.45</v>
       </c>
       <c r="H77" s="9">
-        <v>5.4000000000000003E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="I77" s="10">
-        <v>-97.1</v>
+        <v>-50.1</v>
       </c>
       <c r="J77" s="10">
-        <v>-34.5</v>
+        <v>-98.9</v>
       </c>
       <c r="K77" s="9">
-        <v>0.82399999999999995</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="L77" s="10">
-        <v>-3.35</v>
+        <v>-24.6</v>
       </c>
       <c r="M77" s="9">
-        <v>5.4000000000000003E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="N77" s="10">
-        <v>-97.1</v>
+        <v>-50.1</v>
       </c>
       <c r="O77" s="10">
-        <v>-34.5</v>
+        <v>-98.9</v>
       </c>
       <c r="P77" s="9">
-        <v>0.82399999999999995</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="Q77" s="10">
-        <v>-3.35</v>
+        <v>-24.6</v>
       </c>
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B78" s="7">
-        <v>20.52</v>
+        <v>19.39</v>
       </c>
       <c r="C78" s="7">
-        <v>19.39</v>
+        <v>18.41</v>
       </c>
       <c r="D78" s="7">
-        <v>20.5</v>
+        <v>19.7</v>
       </c>
       <c r="E78" s="7">
-        <v>18.54</v>
+        <v>17.579999999999998</v>
       </c>
       <c r="F78" s="10">
-        <v>-1.1299999999999999</v>
+        <v>-0.98</v>
       </c>
       <c r="G78" s="10">
-        <v>-5.51</v>
+        <v>-5.05</v>
       </c>
       <c r="H78" s="9">
-        <v>0.186</v>
-      </c>
-      <c r="I78" s="8">
-        <v>50259.4</v>
-      </c>
-      <c r="J78" s="8">
-        <v>232812.5</v>
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="I78" s="10">
+        <v>-97.1</v>
+      </c>
+      <c r="J78" s="10">
+        <v>-34.5</v>
       </c>
       <c r="K78" s="9">
-        <v>0.81799999999999995</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="L78" s="10">
-        <v>-3.05</v>
+        <v>-3.35</v>
       </c>
       <c r="M78" s="9">
-        <v>0.186</v>
-      </c>
-      <c r="N78" s="8">
-        <v>50259.4</v>
-      </c>
-      <c r="O78" s="8">
-        <v>232812.5</v>
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="N78" s="10">
+        <v>-97.1</v>
+      </c>
+      <c r="O78" s="10">
+        <v>-34.5</v>
       </c>
       <c r="P78" s="9">
-        <v>0.81799999999999995</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="Q78" s="10">
-        <v>-3.05</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>42491</v>
+        <v>42522</v>
       </c>
       <c r="B79" s="7">
-        <v>21.3</v>
+        <v>20.52</v>
       </c>
       <c r="C79" s="7">
-        <v>20.52</v>
+        <v>19.39</v>
       </c>
       <c r="D79" s="7">
-        <v>22.42</v>
+        <v>20.5</v>
       </c>
       <c r="E79" s="7">
-        <v>19.84</v>
+        <v>18.54</v>
       </c>
       <c r="F79" s="10">
-        <v>-0.78</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="G79" s="10">
-        <v>-3.66</v>
+        <v>-5.51</v>
       </c>
       <c r="H79" s="9">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="I79" s="10">
-        <v>-99.9</v>
+        <v>0.186</v>
+      </c>
+      <c r="I79" s="8">
+        <v>50259.4</v>
       </c>
       <c r="J79" s="8">
-        <v>131.19999999999999</v>
+        <v>232812.5</v>
       </c>
       <c r="K79" s="9">
-        <v>0.63200000000000001</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="L79" s="10">
-        <v>-25.1</v>
+        <v>-3.05</v>
       </c>
       <c r="M79" s="9">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="N79" s="10">
-        <v>-99.9</v>
+        <v>0.186</v>
+      </c>
+      <c r="N79" s="8">
+        <v>50259.4</v>
       </c>
       <c r="O79" s="8">
-        <v>131.19999999999999</v>
+        <v>232812.5</v>
       </c>
       <c r="P79" s="9">
-        <v>0.63200000000000001</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="Q79" s="10">
-        <v>-25.1</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>42461</v>
+        <v>42491</v>
       </c>
       <c r="B80" s="7">
-        <v>19.54</v>
+        <v>21.3</v>
       </c>
       <c r="C80" s="7">
-        <v>21.3</v>
+        <v>20.52</v>
       </c>
       <c r="D80" s="7">
-        <v>21.75</v>
+        <v>22.42</v>
       </c>
       <c r="E80" s="7">
-        <v>18.920000000000002</v>
-      </c>
-      <c r="F80" s="8">
-        <v>1.76</v>
-      </c>
-      <c r="G80" s="8">
-        <v>9.01</v>
+        <v>19.84</v>
+      </c>
+      <c r="F80" s="10">
+        <v>-0.78</v>
+      </c>
+      <c r="G80" s="10">
+        <v>-3.66</v>
       </c>
       <c r="H80" s="9">
-        <v>0.626</v>
-      </c>
-      <c r="I80" s="8">
-        <v>45239.8</v>
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="I80" s="10">
+        <v>-99.9</v>
       </c>
       <c r="J80" s="8">
-        <v>320.8</v>
+        <v>131.19999999999999</v>
       </c>
       <c r="K80" s="9">
-        <v>0.63100000000000001</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="L80" s="10">
-        <v>-25.2</v>
+        <v>-25.1</v>
       </c>
       <c r="M80" s="9">
-        <v>0.626</v>
-      </c>
-      <c r="N80" s="8">
-        <v>45239.8</v>
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="N80" s="10">
+        <v>-99.9</v>
       </c>
       <c r="O80" s="8">
-        <v>320.8</v>
+        <v>131.19999999999999</v>
       </c>
       <c r="P80" s="9">
-        <v>0.63100000000000001</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="Q80" s="10">
-        <v>-25.2</v>
+        <v>-25.1</v>
       </c>
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>42430</v>
+        <v>42461</v>
       </c>
       <c r="B81" s="7">
-        <v>20</v>
+        <v>19.54</v>
       </c>
       <c r="C81" s="7">
-        <v>19.54</v>
+        <v>21.3</v>
       </c>
       <c r="D81" s="7">
-        <v>21.5</v>
+        <v>21.75</v>
       </c>
       <c r="E81" s="7">
-        <v>18.7</v>
-      </c>
-      <c r="F81" s="10">
-        <v>-0.46</v>
-      </c>
-      <c r="G81" s="10">
-        <v>-2.2999999999999998</v>
+        <v>18.920000000000002</v>
+      </c>
+      <c r="F81" s="8">
+        <v>1.76</v>
+      </c>
+      <c r="G81" s="8">
+        <v>9.01</v>
       </c>
       <c r="H81" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="I81" s="10">
-        <v>-31</v>
-      </c>
-      <c r="J81" s="10">
-        <v>-99.6</v>
+        <v>0.626</v>
+      </c>
+      <c r="I81" s="8">
+        <v>45239.8</v>
+      </c>
+      <c r="J81" s="8">
+        <v>320.8</v>
       </c>
       <c r="K81" s="9">
-        <v>5.7999999999999996E-3</v>
+        <v>0.63100000000000001</v>
       </c>
       <c r="L81" s="10">
-        <v>-99.2</v>
+        <v>-25.2</v>
       </c>
       <c r="M81" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="N81" s="10">
-        <v>-31</v>
-      </c>
-      <c r="O81" s="10">
-        <v>-99.6</v>
+        <v>0.626</v>
+      </c>
+      <c r="N81" s="8">
+        <v>45239.8</v>
+      </c>
+      <c r="O81" s="8">
+        <v>320.8</v>
       </c>
       <c r="P81" s="9">
-        <v>5.7999999999999996E-3</v>
+        <v>0.63100000000000001</v>
       </c>
       <c r="Q81" s="10">
-        <v>-99.2</v>
+        <v>-25.2</v>
       </c>
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>42401</v>
+        <v>42430</v>
       </c>
       <c r="B82" s="7">
         <v>20</v>
       </c>
       <c r="C82" s="7">
-        <v>20</v>
+        <v>19.54</v>
       </c>
       <c r="D82" s="7">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="E82" s="7">
-        <v>19.68</v>
-      </c>
-      <c r="F82" s="9">
-        <v>0</v>
-      </c>
-      <c r="G82" s="9">
-        <v>0</v>
+        <v>18.7</v>
+      </c>
+      <c r="F82" s="10">
+        <v>-0.46</v>
+      </c>
+      <c r="G82" s="10">
+        <v>-2.2999999999999998</v>
       </c>
       <c r="H82" s="9">
-        <v>2E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="I82" s="10">
-        <v>-16</v>
+        <v>-31</v>
       </c>
       <c r="J82" s="10">
-        <v>-99.4</v>
+        <v>-99.6</v>
       </c>
       <c r="K82" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="L82" s="10">
-        <v>-98.8</v>
+        <v>-99.2</v>
       </c>
       <c r="M82" s="9">
-        <v>2E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="N82" s="10">
-        <v>-16</v>
+        <v>-31</v>
       </c>
       <c r="O82" s="10">
-        <v>-99.4</v>
+        <v>-99.6</v>
       </c>
       <c r="P82" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="Q82" s="10">
-        <v>-98.8</v>
+        <v>-99.2</v>
       </c>
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>42370</v>
+        <v>42401</v>
       </c>
       <c r="B83" s="7">
-        <v>23.14</v>
+        <v>20</v>
       </c>
       <c r="C83" s="7">
         <v>20</v>
       </c>
       <c r="D83" s="7">
-        <v>23.67</v>
+        <v>20.5</v>
       </c>
       <c r="E83" s="7">
-        <v>19.95</v>
-      </c>
-      <c r="F83" s="10">
-        <v>-3.14</v>
-      </c>
-      <c r="G83" s="10">
-        <v>-13.57</v>
+        <v>19.68</v>
+      </c>
+      <c r="F83" s="9">
+        <v>0</v>
+      </c>
+      <c r="G83" s="9">
+        <v>0</v>
       </c>
       <c r="H83" s="9">
-        <v>2.3999999999999998E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="I83" s="10">
-        <v>-98.5</v>
+        <v>-16</v>
       </c>
       <c r="J83" s="10">
-        <v>-66.2</v>
+        <v>-99.4</v>
       </c>
       <c r="K83" s="9">
-        <v>2.3999999999999998E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="L83" s="10">
-        <v>-66.2</v>
+        <v>-98.8</v>
       </c>
       <c r="M83" s="9">
-        <v>2.3999999999999998E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="N83" s="10">
-        <v>-98.5</v>
+        <v>-16</v>
       </c>
       <c r="O83" s="10">
-        <v>-66.2</v>
+        <v>-99.4</v>
       </c>
       <c r="P83" s="9">
-        <v>2.3999999999999998E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="Q83" s="10">
-        <v>-66.2</v>
+        <v>-98.8</v>
       </c>
     </row>
     <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>42339</v>
+        <v>42370</v>
       </c>
       <c r="B84" s="7">
-        <v>19.399999999999999</v>
+        <v>23.14</v>
       </c>
       <c r="C84" s="7">
-        <v>23.14</v>
+        <v>20</v>
       </c>
       <c r="D84" s="7">
-        <v>24.21</v>
+        <v>23.67</v>
       </c>
       <c r="E84" s="7">
-        <v>19.96</v>
-      </c>
-      <c r="F84" s="8">
-        <v>3.74</v>
-      </c>
-      <c r="G84" s="8">
-        <v>19.28</v>
+        <v>19.95</v>
+      </c>
+      <c r="F84" s="10">
+        <v>-3.14</v>
+      </c>
+      <c r="G84" s="10">
+        <v>-13.57</v>
       </c>
       <c r="H84" s="9">
-        <v>0.16</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="I84" s="10">
-        <v>-81.5</v>
+        <v>-98.5</v>
       </c>
       <c r="J84" s="10">
-        <v>-59.6</v>
+        <v>-66.2</v>
       </c>
       <c r="K84" s="9">
-        <v>2.12</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="L84" s="10">
-        <v>-35.700000000000003</v>
+        <v>-66.2</v>
       </c>
       <c r="M84" s="9">
-        <v>0.16</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="N84" s="10">
-        <v>-81.5</v>
+        <v>-98.5</v>
       </c>
       <c r="O84" s="10">
-        <v>-59.6</v>
+        <v>-66.2</v>
       </c>
       <c r="P84" s="9">
-        <v>2.12</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="Q84" s="10">
-        <v>-35.700000000000003</v>
+        <v>-66.2</v>
       </c>
     </row>
     <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>42309</v>
+        <v>42339</v>
       </c>
       <c r="B85" s="7">
-        <v>24.06</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="C85" s="7">
-        <v>19.399999999999999</v>
+        <v>23.14</v>
       </c>
       <c r="D85" s="7">
-        <v>24.1</v>
+        <v>24.21</v>
       </c>
       <c r="E85" s="7">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="F85" s="10">
-        <v>-4.66</v>
-      </c>
-      <c r="G85" s="10">
-        <v>-19.37</v>
+        <v>19.96</v>
+      </c>
+      <c r="F85" s="8">
+        <v>3.74</v>
+      </c>
+      <c r="G85" s="8">
+        <v>19.28</v>
       </c>
       <c r="H85" s="9">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="I85" s="8">
-        <v>58695.9</v>
-      </c>
-      <c r="J85" s="8">
-        <v>4166</v>
+        <v>0.16</v>
+      </c>
+      <c r="I85" s="10">
+        <v>-81.5</v>
+      </c>
+      <c r="J85" s="10">
+        <v>-59.6</v>
       </c>
       <c r="K85" s="9">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="L85" s="10">
-        <v>-32.4</v>
+        <v>-35.700000000000003</v>
       </c>
       <c r="M85" s="9">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="N85" s="8">
-        <v>58695.9</v>
-      </c>
-      <c r="O85" s="8">
-        <v>4166</v>
+        <v>0.16</v>
+      </c>
+      <c r="N85" s="10">
+        <v>-81.5</v>
+      </c>
+      <c r="O85" s="10">
+        <v>-59.6</v>
       </c>
       <c r="P85" s="9">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="Q85" s="10">
-        <v>-32.4</v>
+        <v>-35.700000000000003</v>
       </c>
     </row>
     <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>42278</v>
+        <v>42309</v>
       </c>
       <c r="B86" s="7">
-        <v>19.79</v>
+        <v>24.06</v>
       </c>
       <c r="C86" s="7">
-        <v>24.06</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="D86" s="7">
-        <v>27.14</v>
+        <v>24.1</v>
       </c>
       <c r="E86" s="7">
-        <v>19.79</v>
-      </c>
-      <c r="F86" s="8">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="G86" s="8">
-        <v>21.58</v>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="F86" s="10">
+        <v>-4.66</v>
+      </c>
+      <c r="G86" s="10">
+        <v>-19.37</v>
       </c>
       <c r="H86" s="9">
-        <v>1.5E-3</v>
+        <v>0.86399999999999999</v>
       </c>
       <c r="I86" s="8">
-        <v>153.4</v>
+        <v>58695.9</v>
       </c>
       <c r="J86" s="8">
-        <v>250</v>
+        <v>4166</v>
       </c>
       <c r="K86" s="9">
-        <v>1.1000000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="L86" s="10">
-        <v>-61.9</v>
+        <v>-32.4</v>
       </c>
       <c r="M86" s="9">
-        <v>1.5E-3</v>
+        <v>0.86399999999999999</v>
       </c>
       <c r="N86" s="8">
-        <v>153.4</v>
+        <v>58695.9</v>
       </c>
       <c r="O86" s="8">
-        <v>250</v>
+        <v>4166</v>
       </c>
       <c r="P86" s="9">
-        <v>1.1000000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="Q86" s="10">
-        <v>-61.9</v>
+        <v>-32.4</v>
       </c>
     </row>
     <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>42248</v>
+        <v>42278</v>
       </c>
       <c r="B87" s="7">
-        <v>17.61</v>
+        <v>19.79</v>
       </c>
       <c r="C87" s="7">
+        <v>24.06</v>
+      </c>
+      <c r="D87" s="7">
+        <v>27.14</v>
+      </c>
+      <c r="E87" s="7">
         <v>19.79</v>
       </c>
-      <c r="D87" s="7">
-        <v>21.54</v>
-      </c>
-      <c r="E87" s="7">
-        <v>17.399999999999999</v>
-      </c>
       <c r="F87" s="8">
-        <v>2.1800000000000002</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="G87" s="8">
-        <v>12.38</v>
+        <v>21.58</v>
       </c>
       <c r="H87" s="9">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="I87" s="10">
-        <v>-99.8</v>
-      </c>
-      <c r="J87" s="10">
-        <v>-73.599999999999994</v>
+        <v>1.5E-3</v>
+      </c>
+      <c r="I87" s="8">
+        <v>153.4</v>
+      </c>
+      <c r="J87" s="8">
+        <v>250</v>
       </c>
       <c r="K87" s="9">
         <v>1.1000000000000001</v>
       </c>
       <c r="L87" s="10">
-        <v>-62</v>
+        <v>-61.9</v>
       </c>
       <c r="M87" s="9">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="N87" s="10">
-        <v>-99.8</v>
-      </c>
-      <c r="O87" s="10">
-        <v>-73.599999999999994</v>
+        <v>1.5E-3</v>
+      </c>
+      <c r="N87" s="8">
+        <v>153.4</v>
+      </c>
+      <c r="O87" s="8">
+        <v>250</v>
       </c>
       <c r="P87" s="9">
         <v>1.1000000000000001</v>
       </c>
       <c r="Q87" s="10">
-        <v>-62</v>
+        <v>-61.9</v>
       </c>
     </row>
     <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>42217</v>
+        <v>42248</v>
       </c>
       <c r="B88" s="7">
-        <v>18.809999999999999</v>
+        <v>17.61</v>
       </c>
       <c r="C88" s="7">
-        <v>17.61</v>
+        <v>19.79</v>
       </c>
       <c r="D88" s="7">
-        <v>22.09</v>
+        <v>21.54</v>
       </c>
       <c r="E88" s="7">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="F88" s="10">
-        <v>-1.2</v>
-      </c>
-      <c r="G88" s="10">
-        <v>-6.38</v>
+        <v>17.399999999999999</v>
+      </c>
+      <c r="F88" s="8">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="G88" s="8">
+        <v>12.38</v>
       </c>
       <c r="H88" s="9">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="I88" s="8">
-        <v>2853.1</v>
-      </c>
-      <c r="J88" s="8">
-        <v>41244.1</v>
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="I88" s="10">
+        <v>-99.8</v>
+      </c>
+      <c r="J88" s="10">
+        <v>-73.599999999999994</v>
       </c>
       <c r="K88" s="9">
         <v>1.1000000000000001</v>
       </c>
       <c r="L88" s="10">
-        <v>-61.9</v>
+        <v>-62</v>
       </c>
       <c r="M88" s="9">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="N88" s="8">
-        <v>2853.1</v>
-      </c>
-      <c r="O88" s="8">
-        <v>41244.1</v>
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="N88" s="10">
+        <v>-99.8</v>
+      </c>
+      <c r="O88" s="10">
+        <v>-73.599999999999994</v>
       </c>
       <c r="P88" s="9">
         <v>1.1000000000000001</v>
       </c>
       <c r="Q88" s="10">
-        <v>-61.9</v>
+        <v>-62</v>
       </c>
     </row>
     <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
-        <v>42186</v>
+        <v>42217</v>
       </c>
       <c r="B89" s="7">
-        <v>26</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="C89" s="7">
-        <v>18.809999999999999</v>
+        <v>17.61</v>
       </c>
       <c r="D89" s="7">
-        <v>26</v>
+        <v>22.09</v>
       </c>
       <c r="E89" s="7">
-        <v>18.100000000000001</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="F89" s="10">
-        <v>-7.19</v>
+        <v>-1.2</v>
       </c>
       <c r="G89" s="10">
-        <v>-27.65</v>
+        <v>-6.38</v>
       </c>
       <c r="H89" s="9">
-        <v>8.3000000000000001E-3</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="I89" s="8">
-        <v>10225</v>
-      </c>
-      <c r="J89" s="10">
-        <v>-98.6</v>
+        <v>2853.1</v>
+      </c>
+      <c r="J89" s="8">
+        <v>41244.1</v>
       </c>
       <c r="K89" s="9">
-        <v>0.85199999999999998</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L89" s="10">
-        <v>-70.400000000000006</v>
+        <v>-61.9</v>
       </c>
       <c r="M89" s="9">
-        <v>8.3000000000000001E-3</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="N89" s="8">
-        <v>10225</v>
-      </c>
-      <c r="O89" s="10">
-        <v>-98.6</v>
+        <v>2853.1</v>
+      </c>
+      <c r="O89" s="8">
+        <v>41244.1</v>
       </c>
       <c r="P89" s="9">
-        <v>0.85199999999999998</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="Q89" s="10">
-        <v>-70.400000000000006</v>
+        <v>-61.9</v>
       </c>
     </row>
     <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
-        <v>42156</v>
+        <v>42186</v>
       </c>
       <c r="B90" s="7">
-        <v>18.45</v>
+        <v>26</v>
       </c>
       <c r="C90" s="7">
+        <v>18.809999999999999</v>
+      </c>
+      <c r="D90" s="7">
         <v>26</v>
       </c>
-      <c r="D90" s="7">
-        <v>32.090000000000003</v>
-      </c>
       <c r="E90" s="7">
-        <v>16.36</v>
-      </c>
-      <c r="F90" s="8">
-        <v>7.55</v>
-      </c>
-      <c r="G90" s="8">
-        <v>40.92</v>
+        <v>18.100000000000001</v>
+      </c>
+      <c r="F90" s="10">
+        <v>-7.19</v>
+      </c>
+      <c r="G90" s="10">
+        <v>-27.65</v>
       </c>
       <c r="H90" s="9">
-        <v>1E-4</v>
-      </c>
-      <c r="I90" s="10">
-        <v>-50</v>
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="I90" s="8">
+        <v>10225</v>
       </c>
       <c r="J90" s="10">
-        <v>-100</v>
+        <v>-98.6</v>
       </c>
       <c r="K90" s="9">
-        <v>0.84399999999999997</v>
+        <v>0.85199999999999998</v>
       </c>
       <c r="L90" s="10">
-        <v>-63</v>
+        <v>-70.400000000000006</v>
       </c>
       <c r="M90" s="9">
-        <v>1E-4</v>
-      </c>
-      <c r="N90" s="10">
-        <v>-50</v>
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="N90" s="8">
+        <v>10225</v>
       </c>
       <c r="O90" s="10">
-        <v>-100</v>
+        <v>-98.6</v>
       </c>
       <c r="P90" s="9">
-        <v>0.84399999999999997</v>
+        <v>0.85199999999999998</v>
       </c>
       <c r="Q90" s="10">
-        <v>-63</v>
+        <v>-70.400000000000006</v>
       </c>
     </row>
     <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
-        <v>42125</v>
+        <v>42156</v>
       </c>
       <c r="B91" s="7">
-        <v>28.8</v>
+        <v>18.45</v>
       </c>
       <c r="C91" s="7">
-        <v>18.45</v>
+        <v>26</v>
       </c>
       <c r="D91" s="7">
-        <v>29.99</v>
+        <v>32.090000000000003</v>
       </c>
       <c r="E91" s="7">
-        <v>17.36</v>
-      </c>
-      <c r="F91" s="10">
-        <v>-10.35</v>
-      </c>
-      <c r="G91" s="10">
-        <v>-35.94</v>
+        <v>16.36</v>
+      </c>
+      <c r="F91" s="8">
+        <v>7.55</v>
+      </c>
+      <c r="G91" s="8">
+        <v>40.92</v>
       </c>
       <c r="H91" s="9">
-        <v>2.0000000000000001E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="I91" s="10">
-        <v>-99.9</v>
+        <v>-50</v>
       </c>
       <c r="J91" s="10">
         <v>-100</v>
@@ -5975,13 +5983,13 @@
         <v>0.84399999999999997</v>
       </c>
       <c r="L91" s="10">
-        <v>-58.9</v>
+        <v>-63</v>
       </c>
       <c r="M91" s="9">
-        <v>2.0000000000000001E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="N91" s="10">
-        <v>-99.9</v>
+        <v>-50</v>
       </c>
       <c r="O91" s="10">
         <v>-100</v>
@@ -5990,330 +5998,330 @@
         <v>0.84399999999999997</v>
       </c>
       <c r="Q91" s="10">
-        <v>-58.9</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
-        <v>42095</v>
+        <v>42125</v>
       </c>
       <c r="B92" s="7">
-        <v>29.01</v>
+        <v>28.8</v>
       </c>
       <c r="C92" s="7">
-        <v>28.8</v>
+        <v>18.45</v>
       </c>
       <c r="D92" s="7">
-        <v>31.99</v>
+        <v>29.99</v>
       </c>
       <c r="E92" s="7">
-        <v>27.8</v>
+        <v>17.36</v>
       </c>
       <c r="F92" s="10">
-        <v>-0.21</v>
+        <v>-10.35</v>
       </c>
       <c r="G92" s="10">
-        <v>-0.72</v>
+        <v>-35.94</v>
       </c>
       <c r="H92" s="9">
-        <v>0.14899999999999999</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="I92" s="10">
-        <v>-54.2</v>
-      </c>
-      <c r="J92" s="8">
-        <v>1826</v>
+        <v>-99.9</v>
+      </c>
+      <c r="J92" s="10">
+        <v>-100</v>
       </c>
       <c r="K92" s="9">
         <v>0.84399999999999997</v>
       </c>
       <c r="L92" s="10">
-        <v>-23.8</v>
+        <v>-58.9</v>
       </c>
       <c r="M92" s="9">
-        <v>0.14899999999999999</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="N92" s="10">
-        <v>-54.2</v>
-      </c>
-      <c r="O92" s="8">
-        <v>1826</v>
+        <v>-99.9</v>
+      </c>
+      <c r="O92" s="10">
+        <v>-100</v>
       </c>
       <c r="P92" s="9">
         <v>0.84399999999999997</v>
       </c>
       <c r="Q92" s="10">
-        <v>-23.8</v>
+        <v>-58.9</v>
       </c>
     </row>
     <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
-        <v>42064</v>
+        <v>42095</v>
       </c>
       <c r="B93" s="7">
-        <v>31.31</v>
+        <v>29.01</v>
       </c>
       <c r="C93" s="7">
-        <v>29.01</v>
+        <v>28.8</v>
       </c>
       <c r="D93" s="7">
-        <v>32.090000000000003</v>
+        <v>31.99</v>
       </c>
       <c r="E93" s="7">
-        <v>28.92</v>
+        <v>27.8</v>
       </c>
       <c r="F93" s="10">
-        <v>-2.2999999999999998</v>
+        <v>-0.21</v>
       </c>
       <c r="G93" s="10">
-        <v>-7.35</v>
+        <v>-0.72</v>
       </c>
       <c r="H93" s="9">
-        <v>0.32500000000000001</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="I93" s="10">
-        <v>-10.5</v>
-      </c>
-      <c r="J93" s="10">
-        <v>-61.6</v>
+        <v>-54.2</v>
+      </c>
+      <c r="J93" s="8">
+        <v>1826</v>
       </c>
       <c r="K93" s="9">
-        <v>0.69499999999999995</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="L93" s="10">
-        <v>-36.799999999999997</v>
+        <v>-23.8</v>
       </c>
       <c r="M93" s="9">
-        <v>0.32500000000000001</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="N93" s="10">
-        <v>-10.5</v>
-      </c>
-      <c r="O93" s="10">
-        <v>-61.6</v>
+        <v>-54.2</v>
+      </c>
+      <c r="O93" s="8">
+        <v>1826</v>
       </c>
       <c r="P93" s="9">
-        <v>0.69499999999999995</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="Q93" s="10">
-        <v>-36.799999999999997</v>
+        <v>-23.8</v>
       </c>
     </row>
     <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
-        <v>42036</v>
+        <v>42064</v>
       </c>
       <c r="B94" s="7">
-        <v>43</v>
+        <v>31.31</v>
       </c>
       <c r="C94" s="7">
-        <v>31.31</v>
+        <v>29.01</v>
       </c>
       <c r="D94" s="7">
-        <v>44.49</v>
+        <v>32.090000000000003</v>
       </c>
       <c r="E94" s="7">
-        <v>30.02</v>
+        <v>28.92</v>
       </c>
       <c r="F94" s="10">
-        <v>-11.69</v>
+        <v>-2.2999999999999998</v>
       </c>
       <c r="G94" s="10">
-        <v>-27.19</v>
+        <v>-7.35</v>
       </c>
       <c r="H94" s="9">
-        <v>0.36299999999999999</v>
-      </c>
-      <c r="I94" s="8">
-        <v>5049.6000000000004</v>
-      </c>
-      <c r="J94" s="8">
-        <v>43.3</v>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="I94" s="10">
+        <v>-10.5</v>
+      </c>
+      <c r="J94" s="10">
+        <v>-61.6</v>
       </c>
       <c r="K94" s="9">
-        <v>0.37</v>
-      </c>
-      <c r="L94" s="8">
-        <v>46.1</v>
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="L94" s="10">
+        <v>-36.799999999999997</v>
       </c>
       <c r="M94" s="9">
-        <v>0.36299999999999999</v>
-      </c>
-      <c r="N94" s="8">
-        <v>5049.6000000000004</v>
-      </c>
-      <c r="O94" s="8">
-        <v>43.3</v>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="N94" s="10">
+        <v>-10.5</v>
+      </c>
+      <c r="O94" s="10">
+        <v>-61.6</v>
       </c>
       <c r="P94" s="9">
-        <v>0.37</v>
-      </c>
-      <c r="Q94" s="8">
-        <v>46.1</v>
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="Q94" s="10">
+        <v>-36.799999999999997</v>
       </c>
     </row>
     <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
-        <v>42005</v>
+        <v>42036</v>
       </c>
       <c r="B95" s="7">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C95" s="7">
-        <v>43</v>
+        <v>31.31</v>
       </c>
       <c r="D95" s="7">
-        <v>46</v>
+        <v>44.49</v>
       </c>
       <c r="E95" s="7">
-        <v>41.82</v>
+        <v>30.02</v>
       </c>
       <c r="F95" s="10">
-        <v>-2</v>
+        <v>-11.69</v>
       </c>
       <c r="G95" s="10">
-        <v>-4.4400000000000004</v>
+        <v>-27.19</v>
       </c>
       <c r="H95" s="9">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="I95" s="10">
-        <v>-98.2</v>
-      </c>
-      <c r="J95" s="9" t="s">
-        <v>17</v>
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="I95" s="8">
+        <v>5049.6000000000004</v>
+      </c>
+      <c r="J95" s="8">
+        <v>43.3</v>
       </c>
       <c r="K95" s="9">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="L95" s="9" t="s">
-        <v>17</v>
+        <v>0.37</v>
+      </c>
+      <c r="L95" s="8">
+        <v>46.1</v>
       </c>
       <c r="M95" s="9">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="N95" s="10">
-        <v>-98.2</v>
-      </c>
-      <c r="O95" s="9" t="s">
-        <v>17</v>
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="N95" s="8">
+        <v>5049.6000000000004</v>
+      </c>
+      <c r="O95" s="8">
+        <v>43.3</v>
       </c>
       <c r="P95" s="9">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="Q95" s="9" t="s">
-        <v>17</v>
+        <v>0.37</v>
+      </c>
+      <c r="Q95" s="8">
+        <v>46.1</v>
       </c>
     </row>
     <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
-        <v>41974</v>
+        <v>42005</v>
       </c>
       <c r="B96" s="7">
-        <v>49.35</v>
+        <v>45</v>
       </c>
       <c r="C96" s="7">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D96" s="7">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E96" s="7">
-        <v>40.39</v>
+        <v>41.82</v>
       </c>
       <c r="F96" s="10">
-        <v>-5.35</v>
+        <v>-2</v>
       </c>
       <c r="G96" s="10">
-        <v>-10.63</v>
+        <v>-4.4400000000000004</v>
       </c>
       <c r="H96" s="9">
-        <v>0.39600000000000002</v>
-      </c>
-      <c r="I96" s="8">
-        <v>1852.9</v>
-      </c>
-      <c r="J96" s="8">
-        <v>372.8</v>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="I96" s="10">
+        <v>-98.2</v>
+      </c>
+      <c r="J96" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K96" s="9">
-        <v>3.3</v>
-      </c>
-      <c r="L96" s="8">
-        <v>470.5</v>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="L96" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M96" s="9">
-        <v>0.39600000000000002</v>
-      </c>
-      <c r="N96" s="8">
-        <v>1852.9</v>
-      </c>
-      <c r="O96" s="8">
-        <v>372.8</v>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="N96" s="10">
+        <v>-98.2</v>
+      </c>
+      <c r="O96" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P96" s="9">
-        <v>3.3</v>
-      </c>
-      <c r="Q96" s="8">
-        <v>470.5</v>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Q96" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
-        <v>41944</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>17</v>
+        <v>41974</v>
+      </c>
+      <c r="B97" s="7">
+        <v>49.35</v>
+      </c>
+      <c r="C97" s="7">
+        <v>45</v>
+      </c>
+      <c r="D97" s="7">
+        <v>70</v>
+      </c>
+      <c r="E97" s="7">
+        <v>40.39</v>
+      </c>
+      <c r="F97" s="10">
+        <v>-5.35</v>
+      </c>
+      <c r="G97" s="10">
+        <v>-10.63</v>
       </c>
       <c r="H97" s="9">
-        <v>2.0299999999999999E-2</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I97" s="8">
-        <v>4723.8</v>
-      </c>
-      <c r="J97" s="10">
-        <v>-84</v>
+        <v>1852.9</v>
+      </c>
+      <c r="J97" s="8">
+        <v>372.8</v>
       </c>
       <c r="K97" s="9">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="L97" s="8">
-        <v>487</v>
+        <v>470.5</v>
       </c>
       <c r="M97" s="9">
-        <v>2.0299999999999999E-2</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="N97" s="8">
-        <v>4723.8</v>
-      </c>
-      <c r="O97" s="10">
-        <v>-84</v>
+        <v>1852.9</v>
+      </c>
+      <c r="O97" s="8">
+        <v>372.8</v>
       </c>
       <c r="P97" s="9">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q97" s="8">
-        <v>487</v>
+        <v>470.5</v>
       </c>
     </row>
     <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
-        <v>41913</v>
+        <v>41944</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>17</v>
@@ -6334,33 +6342,86 @@
         <v>17</v>
       </c>
       <c r="H98" s="9">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="I98" s="8">
+        <v>4723.8</v>
+      </c>
+      <c r="J98" s="10">
+        <v>-84</v>
+      </c>
+      <c r="K98" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="L98" s="8">
+        <v>487</v>
+      </c>
+      <c r="M98" s="9">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="N98" s="8">
+        <v>4723.8</v>
+      </c>
+      <c r="O98" s="10">
+        <v>-84</v>
+      </c>
+      <c r="P98" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="Q98" s="8">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>41913</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H99" s="9">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="I98" s="9" t="s">
+      <c r="I99" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J98" s="10">
+      <c r="J99" s="10">
         <v>-99.2</v>
       </c>
-      <c r="K98" s="9">
+      <c r="K99" s="9">
         <v>2.88</v>
       </c>
-      <c r="L98" s="8">
+      <c r="L99" s="8">
         <v>683.7</v>
       </c>
-      <c r="M98" s="9">
+      <c r="M99" s="9">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="N98" s="9" t="s">
+      <c r="N99" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O98" s="10">
+      <c r="O99" s="10">
         <v>-99.2</v>
       </c>
-      <c r="P98" s="9">
+      <c r="P99" s="9">
         <v>2.88</v>
       </c>
-      <c r="Q98" s="8">
+      <c r="Q99" s="8">
         <v>683.7</v>
       </c>
     </row>
@@ -6379,7 +6440,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>